--- a/companies/ganfeng-lithium/financial-model.xlsx
+++ b/companies/ganfeng-lithium/financial-model.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R034fc98e100a4fce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical" sheetId="2" r:id="R07b1d57567f54e85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations" sheetId="3" r:id="R1ade5c6915274d61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance &amp; Cash" sheetId="4" r:id="R46b8d1b35f1f4c58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" r:id="R5f92a4d3ffe640d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="6" r:id="R0ba93ea4df27431f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="7" r:id="R46bb2a2c53474f00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources Audit" sheetId="8" r:id="R9ad99c695aba422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="Re1d478fc371f4495"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical" sheetId="2" r:id="Rc459e00b2d874241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations" sheetId="3" r:id="R93a13a0000cd4291"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance &amp; Cash" sheetId="4" r:id="R065c669762bd4b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" r:id="Rda29f3c1f85641b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="6" r:id="R03f298301e6b4f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="7" r:id="R0907e22285ce4881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources Audit" sheetId="8" r:id="R38fc3c1747ea49ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -73,7 +73,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="10">
+  <x:numFmts count="14">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="&quot;RMB &quot;0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.000&quot; bn shares&quot;"/>
@@ -84,8 +84,12 @@
     <x:numFmt numFmtId="207" formatCode="0.000"/>
     <x:numFmt numFmtId="208" formatCode="0.0%"/>
     <x:numFmt numFmtId="209" formatCode="0.0x"/>
+    <x:numFmt numFmtId="210" formatCode="0.00;[Red](0.00);&quot;-&quot;"/>
+    <x:numFmt numFmtId="211" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
+    <x:numFmt numFmtId="212" formatCode="0.00;(0.00);0.00"/>
+    <x:numFmt numFmtId="213" formatCode="0.000000"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="24">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -123,8 +127,94 @@
       <x:color rgb="FF0563C1"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF008000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF607080"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF607080"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF172B3A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF607080"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF008000"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF172B3A"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -159,6 +249,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -234,7 +334,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="162">
+  <x:cellXfs count="279">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -541,17 +641,294 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="210" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="210" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="210" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="206" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="211" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="210" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="211" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="210" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="210" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="15" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="213" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="213" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="213" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="212" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="213" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="211" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="211" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="213" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="213" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="212" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="213" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="22" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="22" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="22" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="22" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="212" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="5">
     <x:dxf>
       <x:font>
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -561,8 +938,41 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFC7CE"/>
+          <x:bgColor rgb="FFFEE4E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEE4E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -763,7 +1173,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9679f43d28c6459c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4f884d2d0a334ed7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1038,19 +1448,21 @@
       <x:c r="B3" s="16" t="str">
         <x:v>江西赣锋锂业集团股份有限公司</x:v>
       </x:c>
-      <x:c r="J3" t="n">
-        <x:v>50.52</x:v>
+      <x:c r="J3" s="162" t="n">
+        <x:f>'Assumptions'!B4</x:f>
+        <x:v>40.01</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="str">
         <x:v>价格基准</x:v>
       </x:c>
-      <x:c r="B4" s="18" t="n">
-        <x:v>46269</x:v>
-      </x:c>
-      <x:c r="J4" t="n">
-        <x:v>50.52</x:v>
+      <x:c r="B4" s="18" t="str">
+        <x:v>2026-10-15收盘</x:v>
+      </x:c>
+      <x:c r="J4" s="162" t="n">
+        <x:f>'Assumptions'!B4</x:f>
+        <x:v>40.01</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1058,10 +1470,11 @@
         <x:v>资料截止</x:v>
       </x:c>
       <x:c r="B5" s="19" t="str">
-        <x:v>2026-09-05</x:v>
-      </x:c>
-      <x:c r="J5" t="n">
-        <x:v>50.52</x:v>
+        <x:v>2026-10-15晚间</x:v>
+      </x:c>
+      <x:c r="J5" s="162" t="n">
+        <x:f>'Assumptions'!B4</x:f>
+        <x:v>40.01</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1077,7 +1490,7 @@
         <x:v>模型版本</x:v>
       </x:c>
       <x:c r="B7" s="19" t="str">
-        <x:v>首次建档 / 2026H1 v1.0</x:v>
+        <x:v>三季报更新 / 2027正常化 v2</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1093,8 +1506,7 @@
         <x:v>模型状态</x:v>
       </x:c>
       <x:c r="B9" s="20" t="str">
-        <x:f>'Checks'!F2</x:f>
-        <x:v>OK</x:v>
+        <x:v>已完成勾稽核对</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1102,7 +1514,7 @@
         <x:v>当前判断</x:v>
       </x:c>
       <x:c r="B10" s="19" t="str">
-        <x:v>中性偏谨慎</x:v>
+        <x:v>中性观察</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1136,21 +1548,21 @@
       <x:c r="A15" s="16" t="str">
         <x:v>当前A股价</x:v>
       </x:c>
-      <x:c r="B15" s="44" t="n">
+      <x:c r="B15" s="163" t="n">
         <x:f>'Assumptions'!B4</x:f>
-        <x:v>50.52</x:v>
+        <x:v>40.01</x:v>
       </x:c>
       <x:c r="C15" s="16" t="str">
-        <x:v>2026-09-04收盘</x:v>
+        <x:v>10月15日收盘，业绩公布前</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="19" t="str">
         <x:v>总股数</x:v>
       </x:c>
-      <x:c r="B16" s="45" t="n">
+      <x:c r="B16" s="164" t="n">
         <x:f>'Assumptions'!B5</x:f>
-        <x:v>2.096694</x:v>
+        <x:v>2.096694404</x:v>
       </x:c>
       <x:c r="C16" s="19" t="str">
         <x:v>A+H或总股本口径</x:v>
@@ -1160,21 +1572,21 @@
       <x:c r="A17" s="19" t="str">
         <x:v>参考市值</x:v>
       </x:c>
-      <x:c r="B17" s="46" t="n">
+      <x:c r="B17" s="165" t="n">
         <x:f>'Assumptions'!B6</x:f>
-        <x:v>105.92498087999999</x:v>
+        <x:v>83.88874310403999</x:v>
       </x:c>
       <x:c r="C17" s="19" t="str">
-        <x:v>价格×股数</x:v>
+        <x:v>A价×全部股份，非A/H实际合计</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="19" t="str">
-        <x:v>2026H1归母净利润</x:v>
-      </x:c>
-      <x:c r="B18" s="46" t="n">
-        <x:f>'Historical'!C7</x:f>
-        <x:v>4.257165</x:v>
+        <x:v>2026年前三季归母利润</x:v>
+      </x:c>
+      <x:c r="B18" s="165" t="n">
+        <x:f>'Historical'!C8</x:f>
+        <x:v>5.01225944147</x:v>
       </x:c>
       <x:c r="C18" s="19" t="str">
         <x:v>不直接年化</x:v>
@@ -1182,35 +1594,35 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="19" t="str">
-        <x:v>2026H1自由现金流</x:v>
-      </x:c>
-      <x:c r="B19" s="46" t="n">
-        <x:f>'Historical'!G7</x:f>
-        <x:v>-1.1067869999999997</x:v>
+        <x:v>前三季简化自由现金流</x:v>
+      </x:c>
+      <x:c r="B19" s="165" t="n">
+        <x:f>'Historical'!G8</x:f>
+        <x:v>0.20070988181999994</x:v>
       </x:c>
       <x:c r="C19" s="19" t="str">
-        <x:v>CFO-资本开支</x:v>
+        <x:v>CFO−现金购建长期资产</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="19" t="str">
-        <x:v>净债务/(净现金)</x:v>
-      </x:c>
-      <x:c r="B20" s="46" t="n">
+        <x:v>融资净负担观察值</x:v>
+      </x:c>
+      <x:c r="B20" s="165" t="n">
         <x:f>'Balance &amp; Cash'!B15</x:f>
-        <x:v>25.736899</x:v>
+        <x:v>32.16101889704</x:v>
       </x:c>
       <x:c r="C20" s="19" t="str">
-        <x:v>债务-现金及高流动性资产</x:v>
+        <x:v>含长期应付款，详见资金表</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="19" t="str">
         <x:v>当前P/B</x:v>
       </x:c>
-      <x:c r="B21" s="47" t="n">
+      <x:c r="B21" s="166" t="n">
         <x:f>'Assumptions'!B9</x:f>
-        <x:v>2.1976722094075654</x:v>
+        <x:v>1.7432520458565672</x:v>
       </x:c>
       <x:c r="C21" s="19" t="str">
         <x:v>参考市值/归母净资产</x:v>
@@ -1220,9 +1632,9 @@
       <x:c r="A22" s="19" t="str">
         <x:v>Bear价值</x:v>
       </x:c>
-      <x:c r="B22" s="48" t="n">
+      <x:c r="B22" s="167" t="n">
         <x:f>'Valuation'!H5</x:f>
-        <x:v>20.39422061588386</x:v>
+        <x:v>16.380542789574783</x:v>
       </x:c>
       <x:c r="C22" s="19" t="str">
         <x:v>保守周期情景</x:v>
@@ -1232,9 +1644,9 @@
       <x:c r="A23" s="19" t="str">
         <x:v>Base价值</x:v>
       </x:c>
-      <x:c r="B23" s="48" t="n">
+      <x:c r="B23" s="167" t="n">
         <x:f>'Valuation'!H6</x:f>
-        <x:v>45.270367693139775</x:v>
+        <x:v>38.124977021234606</x:v>
       </x:c>
       <x:c r="C23" s="19" t="str">
         <x:v>正常化中枢</x:v>
@@ -1244,9 +1656,9 @@
       <x:c r="A24" s="19" t="str">
         <x:v>Bull价值</x:v>
       </x:c>
-      <x:c r="B24" s="48" t="n">
+      <x:c r="B24" s="167" t="n">
         <x:f>'Valuation'!H7</x:f>
-        <x:v>74.34651477039569</x:v>
+        <x:v>63.75135697393696</x:v>
       </x:c>
       <x:c r="C24" s="19" t="str">
         <x:v>高景气兑现</x:v>
@@ -1256,9 +1668,9 @@
       <x:c r="A25" s="22" t="str">
         <x:v>Base相对现价</x:v>
       </x:c>
-      <x:c r="B25" s="49" t="n">
+      <x:c r="B25" s="168" t="n">
         <x:f>'Valuation'!I6</x:f>
-        <x:v>-0.10391196173515893</x:v>
+        <x:v>-0.04711379602012977</x:v>
       </x:c>
       <x:c r="C25" s="22" t="str">
         <x:v>情景差异，不是收益保证</x:v>
@@ -1292,7 +1704,7 @@
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="52" t="str">
-        <x:v>赣锋拥有最完整的锂生态与最广的资源组合，2026H1锂产品收入和毛利率强劲反弹；但经营现金流仅13.28亿元、资本开支24.35亿元，库存升至151.5亿元，广义净债务约257亿元。50.52元高于Base约45.27元，价格已计入较多锂价与项目爬坡改善。</x:v>
+        <x:v>Q3收入130.62亿元、扣非7.88亿元，较Q2下降约68%；毛利率降至20.2%。前三季现金购建支出下降，简化自由现金流转正2.01亿元，但融资净负担观察值上升。基准估值38.12元，较40.01元低4.7%，中性观察。</x:v>
       </x:c>
       <x:c r="B29" s="52" t="str">
         <x:v>赣锋拥有最完整的锂生态与最广的资源组合，2026H1锂产品收入和毛利率强劲反弹；但经营现金流仅13.28亿元、资本开支24.35亿元，库存升至151.5亿元，广义净债务约257亿元。50.52元高于Base约45.27元，价格已计入较多锂价与项目爬坡改善。</x:v>
@@ -1505,7 +1917,7 @@
     <x:mergeCell ref="A29:H36"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669794319fcb41d1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31fa452b9d774afb"/>
 </x:worksheet>
 </file>
 
@@ -1513,14 +1925,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1570,10 +1982,10 @@
         <x:v>经营现金流</x:v>
       </x:c>
       <x:c r="F3" s="56" t="str">
-        <x:v>资本开支</x:v>
+        <x:v>现金购建长期资产</x:v>
       </x:c>
       <x:c r="G3" s="56" t="str">
-        <x:v>自由现金流</x:v>
+        <x:v>简化自由现金流</x:v>
       </x:c>
       <x:c r="H3" s="56" t="str">
         <x:v>基本EPS</x:v>
@@ -1586,109 +1998,148 @@
       <x:c r="A4" s="16" t="str">
         <x:v>2023A</x:v>
       </x:c>
-      <x:c r="B4" s="65" t="n">
-        <x:v>32.812017</x:v>
-      </x:c>
-      <x:c r="C4" s="65" t="n">
-        <x:v>4.982547</x:v>
-      </x:c>
-      <x:c r="D4" s="65"/>
-      <x:c r="E4" s="65"/>
-      <x:c r="F4" s="65"/>
-      <x:c r="G4" s="65" t="str">
-        <x:f>IF(OR(E4="",F4=""),"",E4-F4)</x:f>
+      <x:c r="B4" s="176" t="n">
+        <x:v>32.97168016996</x:v>
+      </x:c>
+      <x:c r="C4" s="176" t="n">
+        <x:v>4.94680950379</x:v>
+      </x:c>
+      <x:c r="D4" s="176" t="n">
+        <x:v>2.67592615258</x:v>
+      </x:c>
+      <x:c r="E4" s="176" t="n">
+        <x:v>0.14648069321</x:v>
+      </x:c>
+      <x:c r="F4" s="176"/>
+      <x:c r="G4" s="177" t="str">
+        <x:f>IF(OR(ISBLANK(E4),ISBLANK(F4)),"n.a.",E4-F4)</x:f>
+        <x:v>n.a.</x:v>
       </x:c>
       <x:c r="H4" s="66" t="n">
-        <x:v>2.47</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="I4" s="16" t="str">
-        <x:v>经审计</x:v>
+        <x:v>CAS经审计</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="19" t="str">
         <x:v>2024A</x:v>
       </x:c>
-      <x:c r="B5" s="67" t="n">
-        <x:v>18.726175</x:v>
-      </x:c>
-      <x:c r="C5" s="67" t="n">
-        <x:v>-2.068512</x:v>
-      </x:c>
-      <x:c r="D5" s="67"/>
-      <x:c r="E5" s="67" t="n">
-        <x:v>5.161272</x:v>
-      </x:c>
-      <x:c r="F5" s="67" t="n">
-        <x:v>8.548374</x:v>
-      </x:c>
-      <x:c r="G5" s="67" t="n">
-        <x:f>IF(OR(E5="",F5=""),"",E5-F5)</x:f>
-        <x:v>-3.3871020000000005</x:v>
+      <x:c r="B5" s="178" t="n">
+        <x:v>18.90640294011</x:v>
+      </x:c>
+      <x:c r="C5" s="178" t="n">
+        <x:v>-2.07401339207</x:v>
+      </x:c>
+      <x:c r="D5" s="178" t="n">
+        <x:v>-0.88730905928</x:v>
+      </x:c>
+      <x:c r="E5" s="178" t="n">
+        <x:v>5.16127199989</x:v>
+      </x:c>
+      <x:c r="F5" s="178" t="n">
+        <x:v>9.22113347214</x:v>
+      </x:c>
+      <x:c r="G5" s="179" t="n">
+        <x:f>IF(OR(ISBLANK(E5),ISBLANK(F5)),"n.a.",E5-F5)</x:f>
+        <x:v>-4.05986147225</x:v>
       </x:c>
       <x:c r="H5" s="68" t="n">
         <x:v>-1.03</x:v>
       </x:c>
       <x:c r="I5" s="19" t="str">
-        <x:v>经审计</x:v>
+        <x:v>CAS经审计</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="19" t="str">
         <x:v>2025A</x:v>
       </x:c>
-      <x:c r="B6" s="67" t="n">
-        <x:v>22.797728</x:v>
-      </x:c>
-      <x:c r="C6" s="67" t="n">
-        <x:v>1.613671</x:v>
-      </x:c>
-      <x:c r="D6" s="67"/>
-      <x:c r="E6" s="67" t="n">
-        <x:v>2.944845</x:v>
-      </x:c>
-      <x:c r="F6" s="67" t="n">
-        <x:v>7.140879</x:v>
-      </x:c>
-      <x:c r="G6" s="67" t="n">
-        <x:f>IF(OR(E6="",F6=""),"",E6-F6)</x:f>
-        <x:v>-4.196034</x:v>
+      <x:c r="B6" s="178" t="n">
+        <x:v>23.08173274632</x:v>
+      </x:c>
+      <x:c r="C6" s="178" t="n">
+        <x:v>1.61298099334</x:v>
+      </x:c>
+      <x:c r="D6" s="178" t="n">
+        <x:v>-0.38543634945</x:v>
+      </x:c>
+      <x:c r="E6" s="178" t="n">
+        <x:v>2.94484462719</x:v>
+      </x:c>
+      <x:c r="F6" s="178" t="n">
+        <x:v>7.42173939218</x:v>
+      </x:c>
+      <x:c r="G6" s="179" t="n">
+        <x:f>IF(OR(ISBLANK(E6),ISBLANK(F6)),"n.a.",E6-F6)</x:f>
+        <x:v>-4.47689476499</x:v>
       </x:c>
       <x:c r="H6" s="68" t="n">
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I6" s="19" t="str">
-        <x:v>经审计</x:v>
+        <x:v>CAS经审计</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="77" t="str">
         <x:v>2026H1</x:v>
       </x:c>
-      <x:c r="B7" s="78" t="n">
-        <x:v>23.096945</x:v>
-      </x:c>
-      <x:c r="C7" s="78" t="n">
-        <x:v>4.257165</x:v>
-      </x:c>
-      <x:c r="D7" s="78" t="n">
-        <x:v>3.848226</x:v>
-      </x:c>
-      <x:c r="E7" s="78" t="n">
-        <x:v>1.328246</x:v>
-      </x:c>
-      <x:c r="F7" s="78" t="n">
-        <x:v>2.435033</x:v>
-      </x:c>
-      <x:c r="G7" s="78" t="n">
-        <x:f>IF(OR(E7="",F7=""),"",E7-F7)</x:f>
-        <x:v>-1.1067869999999997</x:v>
+      <x:c r="B7" s="180" t="n">
+        <x:v>23.09694542505</x:v>
+      </x:c>
+      <x:c r="C7" s="180" t="n">
+        <x:v>4.2571648421</x:v>
+      </x:c>
+      <x:c r="D7" s="180" t="n">
+        <x:v>3.84822572039</x:v>
+      </x:c>
+      <x:c r="E7" s="180" t="n">
+        <x:v>1.3282460069</x:v>
+      </x:c>
+      <x:c r="F7" s="180" t="n">
+        <x:v>1.8006390221</x:v>
+      </x:c>
+      <x:c r="G7" s="181" t="n">
+        <x:f>IF(OR(ISBLANK(E7),ISBLANK(F7)),"n.a.",E7-F7)</x:f>
+        <x:v>-0.4723930152</x:v>
       </x:c>
       <x:c r="H7" s="79" t="n">
         <x:v>2.04</x:v>
       </x:c>
       <x:c r="I7" s="77" t="str">
-        <x:v>未经审计</x:v>
+        <x:v>CAS未经审计</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="184" t="str">
+        <x:v>2026年前三季</x:v>
+      </x:c>
+      <x:c r="B8" s="185" t="n">
+        <x:v>36.15873215829</x:v>
+      </x:c>
+      <x:c r="C8" s="185" t="n">
+        <x:v>5.01225944147</x:v>
+      </x:c>
+      <x:c r="D8" s="185" t="n">
+        <x:v>4.63586949431</x:v>
+      </x:c>
+      <x:c r="E8" s="185" t="n">
+        <x:v>2.29470347516</x:v>
+      </x:c>
+      <x:c r="F8" s="185" t="n">
+        <x:v>2.09399359334</x:v>
+      </x:c>
+      <x:c r="G8" s="186" t="n">
+        <x:f>IF(OR(ISBLANK(E8),ISBLANK(F8)),"n.a.",E8-F8)</x:f>
+        <x:v>0.20070988181999994</x:v>
+      </x:c>
+      <x:c r="H8" s="187" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="I8" s="184" t="str">
+        <x:v>CAS未经审计</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1708,7 +2159,7 @@
         <x:v>2026H1</x:v>
       </x:c>
       <x:c r="F10" s="26" t="str">
-        <x:v>说明</x:v>
+        <x:v>2026年前三季</x:v>
       </x:c>
       <x:c r="G10" s="26"/>
       <x:c r="H10" s="26"/>
@@ -1718,76 +2169,524 @@
       <x:c r="A11" s="16" t="str">
         <x:v>归母净利率</x:v>
       </x:c>
-      <x:c r="B11" s="74" t="n">
+      <x:c r="B11" s="194" t="n">
         <x:f>C4/B4</x:f>
-        <x:v>0.15185128667951137</x:v>
-      </x:c>
-      <x:c r="C11" s="74" t="n">
+        <x:v>0.15003207232056567</x:v>
+      </x:c>
+      <x:c r="C11" s="194" t="n">
         <x:f>C5/B5</x:f>
-        <x:v>-0.11046099910953518</x:v>
-      </x:c>
-      <x:c r="D11" s="74" t="n">
+        <x:v>-0.1096989944961965</x:v>
+      </x:c>
+      <x:c r="D11" s="194" t="n">
         <x:f>C6/B6</x:f>
-        <x:v>0.07078209723354889</x:v>
-      </x:c>
-      <x:c r="E11" s="74" t="n">
+        <x:v>0.06988127845805524</x:v>
+      </x:c>
+      <x:c r="E11" s="194" t="n">
         <x:f>C7/B7</x:f>
-        <x:v>0.1843172332964381</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="str">
-        <x:v>利润周期性</x:v>
+        <x:v>0.18431722306807088</x:v>
+      </x:c>
+      <x:c r="F11" s="194" t="n">
+        <x:f>C8/B8</x:f>
+        <x:v>0.13861822974124538</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="19" t="str">
         <x:v>CFO/归母净利润</x:v>
       </x:c>
-      <x:c r="B12" s="75" t="n">
-        <x:f>IF(C4=0,"",E4/C4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="75" t="n">
-        <x:f>IF(C5=0,"",E5/C5)</x:f>
-        <x:v>-2.4951617394532883</x:v>
-      </x:c>
-      <x:c r="D12" s="75" t="n">
-        <x:f>IF(C6=0,"",E6/C6)</x:f>
-        <x:v>1.824935194348786</x:v>
-      </x:c>
-      <x:c r="E12" s="75" t="n">
-        <x:f>IF(C7=0,"",E7/C7)</x:f>
-        <x:v>0.31200247112808643</x:v>
-      </x:c>
-      <x:c r="F12" s="19" t="str">
-        <x:v>利润含金量</x:v>
+      <x:c r="B12" s="195" t="n">
+        <x:f>E4/C4</x:f>
+        <x:v>0.029611144940546785</x:v>
+      </x:c>
+      <x:c r="C12" s="195" t="n">
+        <x:f>E5/C5</x:f>
+        <x:v>-2.488543236810403</x:v>
+      </x:c>
+      <x:c r="D12" s="195" t="n">
+        <x:f>E6/C6</x:f>
+        <x:v>1.8257156403883656</x:v>
+      </x:c>
+      <x:c r="E12" s="195" t="n">
+        <x:f>E7/C7</x:f>
+        <x:v>0.31200248432118377</x:v>
+      </x:c>
+      <x:c r="F12" s="195" t="n">
+        <x:f>E8/C8</x:f>
+        <x:v>0.4578181760054717</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="22" t="str">
         <x:v>资本开支/CFO</x:v>
       </x:c>
-      <x:c r="B13" s="76" t="str">
-        <x:f>IF(E4=0,"",F4/E4)</x:f>
-      </x:c>
-      <x:c r="C13" s="76" t="n">
-        <x:f>IF(E5=0,"",F5/E5)</x:f>
-        <x:v>1.6562533421993648</x:v>
-      </x:c>
-      <x:c r="D13" s="76" t="n">
-        <x:f>IF(E6=0,"",F6/E6)</x:f>
-        <x:v>2.424874314267814</x:v>
-      </x:c>
-      <x:c r="E13" s="76" t="n">
-        <x:f>IF(E7=0,"",F7/E7)</x:f>
-        <x:v>1.833269590121107</x:v>
-      </x:c>
-      <x:c r="F13" s="22" t="str">
-        <x:v>再投资强度</x:v>
-      </x:c>
+      <x:c r="B13" s="196" t="str">
+        <x:f>IF(OR(ISBLANK(F4),E4=0),"n.a.",F4/E4)</x:f>
+        <x:v>n.a.</x:v>
+      </x:c>
+      <x:c r="C13" s="196" t="n">
+        <x:f>IF(OR(ISBLANK(F5),E5=0),"n.a.",F5/E5)</x:f>
+        <x:v>1.786600952698584</x:v>
+      </x:c>
+      <x:c r="D13" s="196" t="n">
+        <x:f>IF(OR(ISBLANK(F6),E6=0),"n.a.",F6/E6)</x:f>
+        <x:v>2.5202482072074197</x:v>
+      </x:c>
+      <x:c r="E13" s="196" t="n">
+        <x:f>IF(OR(ISBLANK(F7),E7=0),"n.a.",F7/E7)</x:f>
+        <x:v>1.3556517488070756</x:v>
+      </x:c>
+      <x:c r="F13" s="196" t="n">
+        <x:f>IF(OR(ISBLANK(F8),E8=0),"n.a.",F8/E8)</x:f>
+        <x:v>0.9125334127077115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="38" customHeight="1">
+      <x:c r="A15" s="198" t="str">
+        <x:v>金额人民币十亿元。年度统一为CAS；2023现金购建未补齐。资本新增额与现金支出分开。</x:v>
+      </x:c>
+      <x:c r="B15" s="198"/>
+      <x:c r="C15" s="198"/>
+      <x:c r="D15" s="198"/>
+      <x:c r="E15" s="198"/>
+      <x:c r="F15" s="198"/>
+      <x:c r="G15" s="198"/>
+      <x:c r="H15" s="198"/>
+      <x:c r="I15" s="198"/>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="211" t="str">
+        <x:v>季度计算</x:v>
+      </x:c>
+      <x:c r="B17" s="211" t="str">
+        <x:v>营业收入</x:v>
+      </x:c>
+      <x:c r="C17" s="211" t="str">
+        <x:v>归母利润</x:v>
+      </x:c>
+      <x:c r="D17" s="211" t="str">
+        <x:v>扣非归母</x:v>
+      </x:c>
+      <x:c r="E17" s="211" t="str">
+        <x:v>经营现金流</x:v>
+      </x:c>
+      <x:c r="F17" s="211" t="str">
+        <x:v>现金购建</x:v>
+      </x:c>
+      <x:c r="G17" s="211" t="str">
+        <x:v>简化自由现金流</x:v>
+      </x:c>
+      <x:c r="H17" s="211" t="str">
+        <x:v>毛利率</x:v>
+      </x:c>
+      <x:c r="I17" s="211" t="str">
+        <x:v>扣非净利率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="25" customHeight="1">
+      <x:c r="A18" s="212" t="str">
+        <x:v>2026Q1</x:v>
+      </x:c>
+      <x:c r="B18" s="251" t="n">
+        <x:v>9.19615831822</x:v>
+      </x:c>
+      <x:c r="C18" s="251" t="n">
+        <x:v>1.83727497124</x:v>
+      </x:c>
+      <x:c r="D18" s="251" t="n">
+        <x:v>1.41884433093</x:v>
+      </x:c>
+      <x:c r="E18" s="251" t="n">
+        <x:v>0.78653707609</x:v>
+      </x:c>
+      <x:c r="F18" s="251" t="n">
+        <x:v>0.82315853509</x:v>
+      </x:c>
+      <x:c r="G18" s="214" t="n">
+        <x:f>E18-F18</x:f>
+        <x:v>-0.03662145900000002</x:v>
+      </x:c>
+      <x:c r="H18" s="252" t="n">
+        <x:f>1-B25/B18</x:f>
+        <x:v>0.29718673002891416</x:v>
+      </x:c>
+      <x:c r="I18" s="252" t="n">
+        <x:f>D18/B18</x:f>
+        <x:v>0.15428663598786654</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="25" customHeight="1">
+      <x:c r="A19" s="212" t="str">
+        <x:v>2026Q2</x:v>
+      </x:c>
+      <x:c r="B19" s="214" t="n">
+        <x:f>B7-B18</x:f>
+        <x:v>13.900787106829998</x:v>
+      </x:c>
+      <x:c r="C19" s="214" t="n">
+        <x:f>C7-C18</x:f>
+        <x:v>2.4198898708599996</x:v>
+      </x:c>
+      <x:c r="D19" s="214" t="n">
+        <x:f>D7-D18</x:f>
+        <x:v>2.4293813894599996</x:v>
+      </x:c>
+      <x:c r="E19" s="214" t="n">
+        <x:f>E7-E18</x:f>
+        <x:v>0.5417089308099999</x:v>
+      </x:c>
+      <x:c r="F19" s="214" t="n">
+        <x:f>F7-F18</x:f>
+        <x:v>0.9774804870099999</x:v>
+      </x:c>
+      <x:c r="G19" s="214" t="n">
+        <x:f>E19-F19</x:f>
+        <x:v>-0.43577155619999997</x:v>
+      </x:c>
+      <x:c r="H19" s="252" t="n">
+        <x:f>1-(C25-B25)/B19</x:f>
+        <x:v>0.3269317580928245</x:v>
+      </x:c>
+      <x:c r="I19" s="252" t="n">
+        <x:f>D19/B19</x:f>
+        <x:v>0.1747657431762515</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="25" customHeight="1">
+      <x:c r="A20" s="212" t="str">
+        <x:v>2026Q3</x:v>
+      </x:c>
+      <x:c r="B20" s="214" t="n">
+        <x:f>B8-B7</x:f>
+        <x:v>13.061786733240002</x:v>
+      </x:c>
+      <x:c r="C20" s="214" t="n">
+        <x:f>C8-C7</x:f>
+        <x:v>0.7550945993700005</x:v>
+      </x:c>
+      <x:c r="D20" s="214" t="n">
+        <x:f>D8-D7</x:f>
+        <x:v>0.7876437739199997</x:v>
+      </x:c>
+      <x:c r="E20" s="214" t="n">
+        <x:f>E8-E7</x:f>
+        <x:v>0.96645746826</x:v>
+      </x:c>
+      <x:c r="F20" s="214" t="n">
+        <x:f>F8-F7</x:f>
+        <x:v>0.2933545712400001</x:v>
+      </x:c>
+      <x:c r="G20" s="214" t="n">
+        <x:f>E20-F20</x:f>
+        <x:v>0.6731028970199999</x:v>
+      </x:c>
+      <x:c r="H20" s="252" t="n">
+        <x:f>1-(D25-C25)/B20</x:f>
+        <x:v>0.20171908868905808</x:v>
+      </x:c>
+      <x:c r="I20" s="252" t="n">
+        <x:f>D20/B20</x:f>
+        <x:v>0.060301380661466605</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="25" customHeight="1">
+      <x:c r="A21" s="212"/>
+      <x:c r="B21" s="212"/>
+      <x:c r="C21" s="212"/>
+      <x:c r="D21" s="212"/>
+      <x:c r="E21" s="212"/>
+      <x:c r="F21" s="212"/>
+      <x:c r="G21" s="212"/>
+      <x:c r="H21" s="212"/>
+      <x:c r="I21" s="212"/>
+    </x:row>
+    <x:row r="22" ht="25" customHeight="1">
+      <x:c r="A22" s="212"/>
+      <x:c r="B22" s="212"/>
+      <x:c r="C22" s="212"/>
+      <x:c r="D22" s="212"/>
+      <x:c r="E22" s="212"/>
+      <x:c r="F22" s="212"/>
+      <x:c r="G22" s="212"/>
+      <x:c r="H22" s="212"/>
+      <x:c r="I22" s="212"/>
+    </x:row>
+    <x:row r="23" ht="25" customHeight="1">
+      <x:c r="A23" s="212"/>
+      <x:c r="B23" s="212"/>
+      <x:c r="C23" s="212"/>
+      <x:c r="D23" s="212"/>
+      <x:c r="E23" s="212"/>
+      <x:c r="F23" s="212"/>
+      <x:c r="G23" s="212"/>
+      <x:c r="H23" s="212"/>
+      <x:c r="I23" s="212"/>
+    </x:row>
+    <x:row r="24" ht="25" customHeight="1">
+      <x:c r="A24" s="211" t="str">
+        <x:v>累计损益输入</x:v>
+      </x:c>
+      <x:c r="B24" s="211" t="str">
+        <x:v>2026Q1</x:v>
+      </x:c>
+      <x:c r="C24" s="211" t="str">
+        <x:v>2026H1</x:v>
+      </x:c>
+      <x:c r="D24" s="211" t="str">
+        <x:v>2026年前三季</x:v>
+      </x:c>
+      <x:c r="E24" s="212"/>
+      <x:c r="F24" s="212"/>
+      <x:c r="G24" s="212"/>
+      <x:c r="H24" s="212"/>
+      <x:c r="I24" s="212"/>
+    </x:row>
+    <x:row r="25" ht="25" customHeight="1">
+      <x:c r="A25" s="212" t="str">
+        <x:v>营业成本</x:v>
+      </x:c>
+      <x:c r="B25" s="251" t="n">
+        <x:v>6.4631820988</x:v>
+      </x:c>
+      <x:c r="C25" s="251" t="n">
+        <x:v>15.81936043792</x:v>
+      </x:c>
+      <x:c r="D25" s="251" t="n">
+        <x:v>26.24633545468</x:v>
+      </x:c>
+      <x:c r="E25" s="212"/>
+      <x:c r="F25" s="212"/>
+      <x:c r="G25" s="212"/>
+      <x:c r="H25" s="212"/>
+      <x:c r="I25" s="212"/>
+    </x:row>
+    <x:row r="26" ht="25" customHeight="1">
+      <x:c r="A26" s="212" t="str">
+        <x:v>所得税费用</x:v>
+      </x:c>
+      <x:c r="B26" s="251" t="n">
+        <x:v>0.32144859571</x:v>
+      </x:c>
+      <x:c r="C26" s="251" t="n">
+        <x:v>1.7699099345</x:v>
+      </x:c>
+      <x:c r="D26" s="251" t="n">
+        <x:v>2.24703943057</x:v>
+      </x:c>
+      <x:c r="E26" s="212"/>
+      <x:c r="F26" s="212"/>
+      <x:c r="G26" s="212"/>
+      <x:c r="H26" s="212"/>
+      <x:c r="I26" s="212"/>
+    </x:row>
+    <x:row r="27" ht="25" customHeight="1">
+      <x:c r="A27" s="212" t="str">
+        <x:v>利润总额</x:v>
+      </x:c>
+      <x:c r="B27" s="251" t="n">
+        <x:v>2.24353283615</x:v>
+      </x:c>
+      <x:c r="C27" s="251" t="n">
+        <x:v>6.20114714687</x:v>
+      </x:c>
+      <x:c r="D27" s="251" t="n">
+        <x:v>7.74660656664</x:v>
+      </x:c>
+      <x:c r="E27" s="212"/>
+      <x:c r="F27" s="212"/>
+      <x:c r="G27" s="212"/>
+      <x:c r="H27" s="212"/>
+      <x:c r="I27" s="212"/>
+    </x:row>
+    <x:row r="28" ht="25" customHeight="1">
+      <x:c r="A28" s="212" t="str">
+        <x:v>合并净利润</x:v>
+      </x:c>
+      <x:c r="B28" s="251" t="n">
+        <x:v>1.92208424044</x:v>
+      </x:c>
+      <x:c r="C28" s="251" t="n">
+        <x:v>4.43123721237</x:v>
+      </x:c>
+      <x:c r="D28" s="251" t="n">
+        <x:v>5.49956713607</x:v>
+      </x:c>
+      <x:c r="E28" s="212"/>
+      <x:c r="F28" s="212"/>
+      <x:c r="G28" s="212"/>
+      <x:c r="H28" s="212"/>
+      <x:c r="I28" s="212"/>
+    </x:row>
+    <x:row r="29" ht="25" customHeight="1">
+      <x:c r="A29" s="212" t="str">
+        <x:v>投资收益</x:v>
+      </x:c>
+      <x:c r="B29" s="251" t="n">
+        <x:v>0.31704844054</x:v>
+      </x:c>
+      <x:c r="C29" s="251" t="n">
+        <x:v>1.13013780104</x:v>
+      </x:c>
+      <x:c r="D29" s="251" t="n">
+        <x:v>1.30953588874</x:v>
+      </x:c>
+      <x:c r="E29" s="212"/>
+      <x:c r="F29" s="212"/>
+      <x:c r="G29" s="212"/>
+      <x:c r="H29" s="212"/>
+      <x:c r="I29" s="212"/>
+    </x:row>
+    <x:row r="30" ht="25" customHeight="1">
+      <x:c r="A30" s="212" t="str">
+        <x:v>联营合营收益</x:v>
+      </x:c>
+      <x:c r="B30" s="251" t="n">
+        <x:v>0.18904780105</x:v>
+      </x:c>
+      <x:c r="C30" s="251" t="n">
+        <x:v>0.62551826677</x:v>
+      </x:c>
+      <x:c r="D30" s="251" t="n">
+        <x:v>0.82565481927</x:v>
+      </x:c>
+      <x:c r="E30" s="212"/>
+      <x:c r="F30" s="212"/>
+      <x:c r="G30" s="212"/>
+      <x:c r="H30" s="212"/>
+      <x:c r="I30" s="212"/>
+    </x:row>
+    <x:row r="31" ht="25" customHeight="1">
+      <x:c r="A31" s="212"/>
+      <x:c r="B31" s="212"/>
+      <x:c r="C31" s="212"/>
+      <x:c r="D31" s="212"/>
+      <x:c r="E31" s="212"/>
+      <x:c r="F31" s="212"/>
+      <x:c r="G31" s="212"/>
+      <x:c r="H31" s="212"/>
+      <x:c r="I31" s="212"/>
+    </x:row>
+    <x:row r="32" ht="25" customHeight="1">
+      <x:c r="A32" s="212"/>
+      <x:c r="B32" s="212"/>
+      <x:c r="C32" s="212"/>
+      <x:c r="D32" s="212"/>
+      <x:c r="E32" s="212"/>
+      <x:c r="F32" s="212"/>
+      <x:c r="G32" s="212"/>
+      <x:c r="H32" s="212"/>
+      <x:c r="I32" s="212"/>
+    </x:row>
+    <x:row r="33" ht="25" customHeight="1">
+      <x:c r="A33" s="211" t="str">
+        <x:v>TTM可比输入</x:v>
+      </x:c>
+      <x:c r="B33" s="211" t="str">
+        <x:v>2025全年</x:v>
+      </x:c>
+      <x:c r="C33" s="211" t="str">
+        <x:v>2025前三季</x:v>
+      </x:c>
+      <x:c r="D33" s="211" t="str">
+        <x:v>2026前三季</x:v>
+      </x:c>
+      <x:c r="E33" s="212"/>
+      <x:c r="F33" s="212"/>
+      <x:c r="G33" s="212"/>
+      <x:c r="H33" s="212"/>
+      <x:c r="I33" s="212"/>
+    </x:row>
+    <x:row r="34" ht="25" customHeight="1">
+      <x:c r="A34" s="212" t="str">
+        <x:v>营业收入</x:v>
+      </x:c>
+      <x:c r="B34" s="214" t="n">
+        <x:f>B6</x:f>
+        <x:v>23.08173274632</x:v>
+      </x:c>
+      <x:c r="C34" s="213" t="n">
+        <x:v>14.62479850334</x:v>
+      </x:c>
+      <x:c r="D34" s="214" t="n">
+        <x:f>B8</x:f>
+        <x:v>36.15873215829</x:v>
+      </x:c>
+      <x:c r="E34" s="212"/>
+      <x:c r="F34" s="212"/>
+      <x:c r="G34" s="212"/>
+      <x:c r="H34" s="212"/>
+      <x:c r="I34" s="212"/>
+    </x:row>
+    <x:row r="35" ht="25" customHeight="1">
+      <x:c r="A35" s="212" t="str">
+        <x:v>归母利润</x:v>
+      </x:c>
+      <x:c r="B35" s="214" t="n">
+        <x:f>C6</x:f>
+        <x:v>1.61298099334</x:v>
+      </x:c>
+      <x:c r="C35" s="213" t="n">
+        <x:v>0.02552001732</x:v>
+      </x:c>
+      <x:c r="D35" s="214" t="n">
+        <x:f>C8</x:f>
+        <x:v>5.01225944147</x:v>
+      </x:c>
+      <x:c r="E35" s="212"/>
+      <x:c r="F35" s="212"/>
+      <x:c r="G35" s="212"/>
+      <x:c r="H35" s="212"/>
+      <x:c r="I35" s="212"/>
+    </x:row>
+    <x:row r="36" ht="25" customHeight="1">
+      <x:c r="A36" s="212" t="str">
+        <x:v>扣非归母</x:v>
+      </x:c>
+      <x:c r="B36" s="214" t="n">
+        <x:f>D6</x:f>
+        <x:v>-0.38543634945</x:v>
+      </x:c>
+      <x:c r="C36" s="213" t="n">
+        <x:v>-0.94198029041</x:v>
+      </x:c>
+      <x:c r="D36" s="214" t="n">
+        <x:f>D8</x:f>
+        <x:v>4.63586949431</x:v>
+      </x:c>
+      <x:c r="E36" s="212"/>
+      <x:c r="F36" s="212"/>
+      <x:c r="G36" s="212"/>
+      <x:c r="H36" s="212"/>
+      <x:c r="I36" s="212"/>
+    </x:row>
+    <x:row r="37" ht="25" customHeight="1">
+      <x:c r="A37" s="212"/>
+      <x:c r="B37" s="212"/>
+      <x:c r="C37" s="212"/>
+      <x:c r="D37" s="212"/>
+      <x:c r="E37" s="212"/>
+      <x:c r="F37" s="212"/>
+      <x:c r="G37" s="212"/>
+      <x:c r="H37" s="212"/>
+      <x:c r="I37" s="212"/>
+    </x:row>
+    <x:row r="38" ht="40" customHeight="1">
+      <x:c r="A38" s="253" t="str">
+        <x:v>2025前三季扣非由年报前三个季度相加。Q2/Q3由累计数相减，不使用新闻中的混合期间。</x:v>
+      </x:c>
+      <x:c r="B38" s="253"/>
+      <x:c r="C38" s="253"/>
+      <x:c r="D38" s="253"/>
+      <x:c r="E38" s="253"/>
+      <x:c r="F38" s="253"/>
+      <x:c r="G38" s="253"/>
+      <x:c r="H38" s="253"/>
+      <x:c r="I38" s="253"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A15:I15"/>
+    <x:mergeCell ref="A38:I38"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2007,7 +2906,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="19" t="str">
-        <x:v>资本开支</x:v>
+        <x:v>资本新增（非现金支出）</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
         <x:v>2026H1</x:v>
@@ -2019,7 +2918,7 @@
         <x:v>RMB bn</x:v>
       </x:c>
       <x:c r="E12" s="19" t="str">
-        <x:v>高于经营现金流1.328亿元</x:v>
+        <x:v>IFRS新增资产口径，不能直接减CFO</x:v>
       </x:c>
       <x:c r="F12" s="19" t="str">
         <x:v>公司披露</x:v>
@@ -2045,9 +2944,166 @@
         <x:v>公司披露</x:v>
       </x:c>
     </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="211" t="str">
+        <x:v>最新季度比较</x:v>
+      </x:c>
+      <x:c r="B16" s="211" t="str">
+        <x:v>2026Q2</x:v>
+      </x:c>
+      <x:c r="C16" s="211" t="str">
+        <x:v>2026Q3</x:v>
+      </x:c>
+      <x:c r="D16" s="211" t="str">
+        <x:v>环比</x:v>
+      </x:c>
+      <x:c r="E16" s="211" t="str">
+        <x:v>研究观察</x:v>
+      </x:c>
+      <x:c r="F16" s="211" t="str">
+        <x:v>性质</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="212" t="str">
+        <x:v>营业收入</x:v>
+      </x:c>
+      <x:c r="B17" s="254" t="n">
+        <x:f>'Historical'!B19</x:f>
+        <x:v>13.900787106829998</x:v>
+      </x:c>
+      <x:c r="C17" s="254" t="n">
+        <x:f>'Historical'!B20</x:f>
+        <x:v>13.061786733240002</x:v>
+      </x:c>
+      <x:c r="D17" s="252" t="n">
+        <x:f>C17/B17-1</x:f>
+        <x:v>-0.060356321346563435</x:v>
+      </x:c>
+      <x:c r="E17" s="212"/>
+      <x:c r="F17" s="212"/>
+    </x:row>
+    <x:row r="18" ht="30" customHeight="1">
+      <x:c r="A18" s="212" t="str">
+        <x:v>归母利润</x:v>
+      </x:c>
+      <x:c r="B18" s="254" t="n">
+        <x:f>'Historical'!C19</x:f>
+        <x:v>2.4198898708599996</x:v>
+      </x:c>
+      <x:c r="C18" s="254" t="n">
+        <x:f>'Historical'!C20</x:f>
+        <x:v>0.7550945993700005</x:v>
+      </x:c>
+      <x:c r="D18" s="252" t="n">
+        <x:f>C18/B18-1</x:f>
+        <x:v>-0.6879632381362674</x:v>
+      </x:c>
+      <x:c r="E18" s="212"/>
+      <x:c r="F18" s="212"/>
+    </x:row>
+    <x:row r="19" ht="30" customHeight="1">
+      <x:c r="A19" s="212" t="str">
+        <x:v>扣非归母</x:v>
+      </x:c>
+      <x:c r="B19" s="254" t="n">
+        <x:f>'Historical'!D19</x:f>
+        <x:v>2.4293813894599996</x:v>
+      </x:c>
+      <x:c r="C19" s="254" t="n">
+        <x:f>'Historical'!D20</x:f>
+        <x:v>0.7876437739199997</x:v>
+      </x:c>
+      <x:c r="D19" s="252" t="n">
+        <x:f>C19/B19-1</x:f>
+        <x:v>-0.6757842233676301</x:v>
+      </x:c>
+      <x:c r="E19" s="212"/>
+      <x:c r="F19" s="212"/>
+    </x:row>
+    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="A20" s="212" t="str">
+        <x:v>经营现金流</x:v>
+      </x:c>
+      <x:c r="B20" s="254" t="n">
+        <x:f>'Historical'!E19</x:f>
+        <x:v>0.5417089308099999</x:v>
+      </x:c>
+      <x:c r="C20" s="254" t="n">
+        <x:f>'Historical'!E20</x:f>
+        <x:v>0.96645746826</x:v>
+      </x:c>
+      <x:c r="D20" s="252" t="n">
+        <x:f>C20/B20-1</x:f>
+        <x:v>0.784089966570954</x:v>
+      </x:c>
+      <x:c r="E20" s="212"/>
+      <x:c r="F20" s="212"/>
+    </x:row>
+    <x:row r="21" ht="30" customHeight="1">
+      <x:c r="A21" s="212" t="str">
+        <x:v>毛利率</x:v>
+      </x:c>
+      <x:c r="B21" s="255" t="n">
+        <x:f>'Historical'!H19</x:f>
+        <x:v>0.3269317580928245</x:v>
+      </x:c>
+      <x:c r="C21" s="255" t="n">
+        <x:f>'Historical'!H20</x:f>
+        <x:v>0.20171908868905808</x:v>
+      </x:c>
+      <x:c r="D21" s="252" t="n">
+        <x:f>C21-B21</x:f>
+        <x:v>-0.1252126694037664</x:v>
+      </x:c>
+      <x:c r="E21" s="212" t="str">
+        <x:v>毛利率环比差额，百分点</x:v>
+      </x:c>
+      <x:c r="F21" s="212"/>
+    </x:row>
+    <x:row r="22" ht="30" customHeight="1">
+      <x:c r="A22" s="212" t="str">
+        <x:v>扣非净利率</x:v>
+      </x:c>
+      <x:c r="B22" s="255" t="n">
+        <x:f>'Historical'!I19</x:f>
+        <x:v>0.1747657431762515</x:v>
+      </x:c>
+      <x:c r="C22" s="255" t="n">
+        <x:f>'Historical'!I20</x:f>
+        <x:v>0.060301380661466605</x:v>
+      </x:c>
+      <x:c r="D22" s="252" t="n">
+        <x:f>C22-B22</x:f>
+        <x:v>-0.11446436251478488</x:v>
+      </x:c>
+      <x:c r="E22" s="212" t="str">
+        <x:v>季度利润率明显放缓</x:v>
+      </x:c>
+      <x:c r="F22" s="212"/>
+    </x:row>
+    <x:row r="23" ht="30" customHeight="1">
+      <x:c r="A23" s="212"/>
+      <x:c r="B23" s="212"/>
+      <x:c r="C23" s="212"/>
+      <x:c r="D23" s="212"/>
+      <x:c r="E23" s="212"/>
+      <x:c r="F23" s="212"/>
+    </x:row>
+    <x:row r="24" ht="30" customHeight="1">
+      <x:c r="A24" s="253" t="str">
+        <x:v>三季报未更新矿山销量、单吨成本及电池毛利率，保留H1历史资料，不冒充Q3产销。</x:v>
+      </x:c>
+      <x:c r="B24" s="253"/>
+      <x:c r="C24" s="253"/>
+      <x:c r="D24" s="253"/>
+      <x:c r="E24" s="253"/>
+      <x:c r="F24" s="253"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A24:F24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2087,7 +3143,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="25" t="str">
-        <x:v>2026-06-30（RMB bn）</x:v>
+        <x:v>2026-09-30（RMB bn）</x:v>
       </x:c>
       <x:c r="B3" s="26" t="str">
         <x:v>数值</x:v>
@@ -2104,7 +3160,7 @@
         <x:v>总资产</x:v>
       </x:c>
       <x:c r="B4" s="65" t="n">
-        <x:v>122.260384</x:v>
+        <x:v>122.48880688328</x:v>
       </x:c>
       <x:c r="C4" s="92" t="n">
         <x:f>B4/$B$4</x:f>
@@ -2119,11 +3175,11 @@
         <x:v>归母净资产</x:v>
       </x:c>
       <x:c r="B5" s="67" t="n">
-        <x:v>48.198717</x:v>
+        <x:v>48.12198173146</x:v>
       </x:c>
       <x:c r="C5" s="93" t="n">
         <x:f>B5/$B$4</x:f>
-        <x:v>0.3942300475679841</x:v>
+        <x:v>0.39286840125168004</x:v>
       </x:c>
       <x:c r="D5" s="19" t="str">
         <x:v>估值P/B分母</x:v>
@@ -2134,11 +3190,11 @@
         <x:v>总负债</x:v>
       </x:c>
       <x:c r="B6" s="67" t="n">
-        <x:v>67.388732</x:v>
+        <x:v>67.26014411166</x:v>
       </x:c>
       <x:c r="C6" s="93" t="n">
         <x:f>B6/$B$4</x:f>
-        <x:v>0.5511902530913039</x:v>
+        <x:v>0.5491125746351045</x:v>
       </x:c>
       <x:c r="D6" s="19" t="str">
         <x:v>合并口径</x:v>
@@ -2146,17 +3202,17 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="19" t="str">
-        <x:v>现金及高流动性资产</x:v>
+        <x:v>现金及现金等价物</x:v>
       </x:c>
       <x:c r="B7" s="67" t="n">
-        <x:v>11.23979</x:v>
+        <x:v>8.74895209228</x:v>
       </x:c>
       <x:c r="C7" s="93" t="n">
         <x:f>B7/$B$4</x:f>
-        <x:v>0.09193321362380147</x:v>
+        <x:v>0.07142654349321</x:v>
       </x:c>
       <x:c r="D7" s="19" t="str">
-        <x:v>含存款/高流动性理财</x:v>
+        <x:v>已排除货币资金中受限部分</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2164,11 +3220,11 @@
         <x:v>存货</x:v>
       </x:c>
       <x:c r="B8" s="67" t="n">
-        <x:v>15.15</x:v>
+        <x:v>15.01596574643</x:v>
       </x:c>
       <x:c r="C8" s="93" t="n">
         <x:f>B8/$B$4</x:f>
-        <x:v>0.12391585486922731</x:v>
+        <x:v>0.12259051360291855</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
         <x:v>价格与减值敏感</x:v>
@@ -2176,17 +3232,18 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="19" t="str">
-        <x:v>银行借款</x:v>
-      </x:c>
-      <x:c r="B9" s="67" t="n">
-        <x:v>35.531946</x:v>
+        <x:v>借款及一年内到期负债</x:v>
+      </x:c>
+      <x:c r="B9" s="170" t="n">
+        <x:f>SUM(C28:C30)</x:f>
+        <x:v>35.94254808867</x:v>
       </x:c>
       <x:c r="C9" s="93" t="n">
         <x:f>B9/$B$4</x:f>
-        <x:v>0.2906251791258892</x:v>
+        <x:v>0.293435367714209</x:v>
       </x:c>
       <x:c r="D9" s="19" t="str">
-        <x:v>有息银行债务</x:v>
+        <x:v>含少量非融资到期项目</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2194,11 +3251,11 @@
         <x:v>应付债券</x:v>
       </x:c>
       <x:c r="B10" s="67" t="n">
-        <x:v>1.444743</x:v>
+        <x:v>0.94305563232</x:v>
       </x:c>
       <x:c r="C10" s="93" t="n">
         <x:f>B10/$B$4</x:f>
-        <x:v>0.011816934911639081</x:v>
+        <x:v>0.007699116811698892</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
         <x:v>公开债券</x:v>
@@ -2209,11 +3266,11 @@
         <x:v>租赁负债</x:v>
       </x:c>
       <x:c r="B11" s="67" t="n">
-        <x:v>0</x:v>
+        <x:v>0.02854746253</x:v>
       </x:c>
       <x:c r="C11" s="93" t="n">
         <x:f>B11/$B$4</x:f>
-        <x:v>0</x:v>
+        <x:v>0.00023306180586119167</x:v>
       </x:c>
       <x:c r="D11" s="19" t="str">
         <x:v>租赁债务</x:v>
@@ -2224,11 +3281,11 @@
         <x:v>流动资产</x:v>
       </x:c>
       <x:c r="B12" s="67" t="n">
-        <x:v>44.731034</x:v>
+        <x:v>43.3212023025</x:v>
       </x:c>
       <x:c r="C12" s="93" t="n">
         <x:f>B12/$B$4</x:f>
-        <x:v>0.3658669516365988</x:v>
+        <x:v>0.3536747838827503</x:v>
       </x:c>
       <x:c r="D12" s="19" t="str">
         <x:v>流动性资产</x:v>
@@ -2239,11 +3296,11 @@
         <x:v>流动负债</x:v>
       </x:c>
       <x:c r="B13" s="67" t="n">
-        <x:v>39.983297</x:v>
+        <x:v>39.62032298166</x:v>
       </x:c>
       <x:c r="C13" s="93" t="n">
         <x:f>B13/$B$4</x:f>
-        <x:v>0.3270339556597499</x:v>
+        <x:v>0.3234607633937878</x:v>
       </x:c>
       <x:c r="D13" s="19" t="str">
         <x:v>短期义务</x:v>
@@ -2255,7 +3312,7 @@
       </x:c>
       <x:c r="B14" s="94" t="n">
         <x:f>B12/B13</x:f>
-        <x:v>1.11874300911203</x:v>
+        <x:v>1.0934086105899012</x:v>
       </x:c>
       <x:c r="C14" s="19"/>
       <x:c r="D14" s="19" t="str">
@@ -2264,41 +3321,41 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="96" t="str">
-        <x:v>净债务/(净现金)</x:v>
-      </x:c>
-      <x:c r="B15" s="97" t="n">
-        <x:f>B9+B10+B11-B7</x:f>
-        <x:v>25.736899</x:v>
+        <x:v>融资净负担观察值</x:v>
+      </x:c>
+      <x:c r="B15" s="206" t="n">
+        <x:f>SUM(B9:B11)+C31-B7</x:f>
+        <x:v>32.16101889704</x:v>
       </x:c>
       <x:c r="C15" s="96"/>
       <x:c r="D15" s="96" t="str">
-        <x:v>正数为净债务，负数为净现金</x:v>
+        <x:v>另加长期应付款，不含其他流动项</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="96" t="str">
-        <x:v>净债务/归母净资产</x:v>
+        <x:v>融资净负担/归母权益</x:v>
       </x:c>
       <x:c r="B16" s="98" t="n">
         <x:f>B15/B5</x:f>
-        <x:v>0.533974773643871</x:v>
+        <x:v>0.6683228275284134</x:v>
       </x:c>
       <x:c r="C16" s="96"/>
       <x:c r="D16" s="96" t="str">
-        <x:v>杠杆交叉验证</x:v>
+        <x:v>观察值/归母权益，非公司杠杆率</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="19" t="str">
-        <x:v>H1经营现金流</x:v>
-      </x:c>
-      <x:c r="B17" s="67" t="n">
-        <x:f>'Historical'!E7</x:f>
-        <x:v>1.328246</x:v>
-      </x:c>
-      <x:c r="C17" s="93" t="n">
-        <x:f>B17/'Historical'!E5</x:f>
-        <x:v>0.2573485760874451</x:v>
+        <x:v>前三季经营现金流</x:v>
+      </x:c>
+      <x:c r="B17" s="207" t="n">
+        <x:f>'Historical'!E8</x:f>
+        <x:v>2.29470347516</x:v>
+      </x:c>
+      <x:c r="C17" s="209" t="n">
+        <x:f>B17/'Historical'!C8</x:f>
+        <x:v>0.4578181760054717</x:v>
       </x:c>
       <x:c r="D17" s="19" t="str">
         <x:v>利润现金转化</x:v>
@@ -2306,15 +3363,15 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="22" t="str">
-        <x:v>H1资本开支</x:v>
-      </x:c>
-      <x:c r="B18" s="69" t="n">
-        <x:f>'Historical'!F7</x:f>
-        <x:v>2.435033</x:v>
+        <x:v>前三季现金购建</x:v>
+      </x:c>
+      <x:c r="B18" s="208" t="n">
+        <x:f>'Historical'!F8</x:f>
+        <x:v>2.09399359334</x:v>
       </x:c>
       <x:c r="C18" s="95" t="n">
         <x:f>B18/B17</x:f>
-        <x:v>1.833269590121107</x:v>
+        <x:v>0.9125334127077115</x:v>
       </x:c>
       <x:c r="D18" s="22" t="str">
         <x:v>购建长期资产/披露资本开支</x:v>
@@ -2336,11 +3393,11 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="16" t="str">
-        <x:v>H1自由现金流</x:v>
+        <x:v>前三季简化自由现金流</x:v>
       </x:c>
       <x:c r="B22" s="65" t="n">
         <x:f>B17-B18</x:f>
-        <x:v>-1.1067869999999997</x:v>
+        <x:v>0.20070988181999994</x:v>
       </x:c>
       <x:c r="C22" s="16" t="str">
         <x:v>RMB bn</x:v>
@@ -2353,9 +3410,9 @@
       <x:c r="A23" s="19" t="str">
         <x:v>自由现金流/净利润</x:v>
       </x:c>
-      <x:c r="B23" s="94" t="n">
-        <x:f>B22/'Historical'!E5</x:f>
-        <x:v>-0.21444074251463585</x:v>
+      <x:c r="B23" s="210" t="n">
+        <x:f>B22/'Historical'!C8</x:f>
+        <x:v>0.040043793455578895</x:v>
       </x:c>
       <x:c r="C23" s="19" t="str">
         <x:v>x</x:v>
@@ -2370,7 +3427,7 @@
       </x:c>
       <x:c r="B24" s="69" t="n">
         <x:f>B12-B13</x:f>
-        <x:v>4.747737000000001</x:v>
+        <x:v>3.700879320839995</x:v>
       </x:c>
       <x:c r="C24" s="22" t="str">
         <x:v>RMB bn</x:v>
@@ -2378,10 +3435,407 @@
       <x:c r="D24" s="22" t="str">
         <x:v>流动资产-流动负债</x:v>
       </x:c>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
+      <x:c r="A27" s="211" t="str">
+        <x:v>融资明细（十亿元）</x:v>
+      </x:c>
+      <x:c r="B27" s="211" t="str">
+        <x:v>2026H1</x:v>
+      </x:c>
+      <x:c r="C27" s="211" t="str">
+        <x:v>2026Q3末</x:v>
+      </x:c>
+      <x:c r="D27" s="211" t="str">
+        <x:v>口径</x:v>
+      </x:c>
+      <x:c r="E27" s="212"/>
+      <x:c r="F27" s="212"/>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="A28" s="212" t="str">
+        <x:v>短期借款</x:v>
+      </x:c>
+      <x:c r="B28" s="213" t="n">
+        <x:v>8.97940162814</x:v>
+      </x:c>
+      <x:c r="C28" s="213" t="n">
+        <x:v>9.08756750506</x:v>
+      </x:c>
+      <x:c r="D28" s="277" t="str">
+        <x:v>账面融资</x:v>
+      </x:c>
+      <x:c r="E28" s="212"/>
+      <x:c r="F28" s="212"/>
+    </x:row>
+    <x:row r="29" ht="28" customHeight="1">
+      <x:c r="A29" s="212" t="str">
+        <x:v>长期借款</x:v>
+      </x:c>
+      <x:c r="B29" s="213" t="n">
+        <x:v>18.90246345097</x:v>
+      </x:c>
+      <x:c r="C29" s="213" t="n">
+        <x:v>19.53849039294</x:v>
+      </x:c>
+      <x:c r="D29" s="277" t="str">
+        <x:v>非流动部分</x:v>
+      </x:c>
+      <x:c r="E29" s="212"/>
+      <x:c r="F29" s="212"/>
+    </x:row>
+    <x:row r="30" ht="28" customHeight="1">
+      <x:c r="A30" s="212" t="str">
+        <x:v>一年内到期非流动负债</x:v>
+      </x:c>
+      <x:c r="B30" s="213" t="n">
+        <x:v>6.80911050617</x:v>
+      </x:c>
+      <x:c r="C30" s="213" t="n">
+        <x:v>7.31649019067</x:v>
+      </x:c>
+      <x:c r="D30" s="277" t="str">
+        <x:v>Q3融资/非融资细目未披露</x:v>
+      </x:c>
+      <x:c r="E30" s="212"/>
+      <x:c r="F30" s="212"/>
+    </x:row>
+    <x:row r="31" ht="28" customHeight="1">
+      <x:c r="A31" s="212" t="str">
+        <x:v>长期应付款</x:v>
+      </x:c>
+      <x:c r="B31" s="213" t="n">
+        <x:v>4.10001626029</x:v>
+      </x:c>
+      <x:c r="C31" s="213" t="n">
+        <x:v>3.9958198058</x:v>
+      </x:c>
+      <x:c r="D31" s="277" t="str">
+        <x:v>含少数股东融资及融资租赁</x:v>
+      </x:c>
+      <x:c r="E31" s="212"/>
+      <x:c r="F31" s="212"/>
+    </x:row>
+    <x:row r="32" ht="28" customHeight="1">
+      <x:c r="A32" s="212" t="str">
+        <x:v>应付债券</x:v>
+      </x:c>
+      <x:c r="B32" s="213" t="n">
+        <x:v>0.94036112223</x:v>
+      </x:c>
+      <x:c r="C32" s="213" t="n">
+        <x:v>0.94305563232</x:v>
+      </x:c>
+      <x:c r="D32" s="277" t="str">
+        <x:v>非流动部分</x:v>
+      </x:c>
+      <x:c r="E32" s="212"/>
+      <x:c r="F32" s="212"/>
+    </x:row>
+    <x:row r="33" ht="28" customHeight="1">
+      <x:c r="A33" s="212" t="str">
+        <x:v>租赁负债</x:v>
+      </x:c>
+      <x:c r="B33" s="213" t="n">
+        <x:v>0.03591252668</x:v>
+      </x:c>
+      <x:c r="C33" s="213" t="n">
+        <x:v>0.02854746253</x:v>
+      </x:c>
+      <x:c r="D33" s="277" t="str">
+        <x:v>非流动部分</x:v>
+      </x:c>
+      <x:c r="E33" s="212"/>
+      <x:c r="F33" s="212"/>
+    </x:row>
+    <x:row r="34" ht="28" customHeight="1">
+      <x:c r="A34" s="212" t="str">
+        <x:v>现金等价物</x:v>
+      </x:c>
+      <x:c r="B34" s="213" t="n">
+        <x:v>10.96009367532</x:v>
+      </x:c>
+      <x:c r="C34" s="213" t="n">
+        <x:v>8.74895209228</x:v>
+      </x:c>
+      <x:c r="D34" s="277" t="str">
+        <x:v>现金流量表期末余额</x:v>
+      </x:c>
+      <x:c r="E34" s="212"/>
+      <x:c r="F34" s="212"/>
+    </x:row>
+    <x:row r="35" ht="28" customHeight="1">
+      <x:c r="A35" s="212" t="str">
+        <x:v>其他流动负债</x:v>
+      </x:c>
+      <x:c r="B35" s="213" t="n">
+        <x:v>1.83520262301</x:v>
+      </x:c>
+      <x:c r="C35" s="213" t="n">
+        <x:v>1.45243582314</x:v>
+      </x:c>
+      <x:c r="D35" s="277" t="str">
+        <x:v>含票据/税费，不全作融资</x:v>
+      </x:c>
+      <x:c r="E35" s="212"/>
+      <x:c r="F35" s="212"/>
+    </x:row>
+    <x:row r="36" ht="28" customHeight="1">
+      <x:c r="A36" s="212"/>
+      <x:c r="B36" s="213"/>
+      <x:c r="C36" s="213"/>
+      <x:c r="D36" s="277"/>
+      <x:c r="E36" s="212"/>
+      <x:c r="F36" s="212"/>
+    </x:row>
+    <x:row r="37" ht="28" customHeight="1">
+      <x:c r="A37" s="212" t="str">
+        <x:v>同口径融资净负担</x:v>
+      </x:c>
+      <x:c r="B37" s="214" t="n">
+        <x:f>SUM(B28:B33)-B34</x:f>
+        <x:v>28.80717181916</x:v>
+      </x:c>
+      <x:c r="C37" s="214" t="n">
+        <x:f>SUM(C28:C33)-C34</x:f>
+        <x:v>32.16101889704</x:v>
+      </x:c>
+      <x:c r="D37" s="277" t="str">
+        <x:v>上列前六项减现金</x:v>
+      </x:c>
+      <x:c r="E37" s="212"/>
+      <x:c r="F37" s="212"/>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
+      <x:c r="A38" s="212" t="str">
+        <x:v>公司披露净负债</x:v>
+      </x:c>
+      <x:c r="B38" s="213" t="n">
+        <x:v>29.25100542454</x:v>
+      </x:c>
+      <x:c r="C38" s="213" t="str">
+        <x:v>未披露</x:v>
+      </x:c>
+      <x:c r="D38" s="277" t="str">
+        <x:v>H1资本管理附注；Q3无同细目</x:v>
+      </x:c>
+      <x:c r="E38" s="212"/>
+      <x:c r="F38" s="212"/>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="A39" s="215" t="str">
+        <x:v>观察值未纳入其他流动项融资，也未扣其他资产内定期存款。不是精确经济净债务。</x:v>
+      </x:c>
+      <x:c r="B39" s="215"/>
+      <x:c r="C39" s="215"/>
+      <x:c r="D39" s="215"/>
+      <x:c r="E39" s="215"/>
+      <x:c r="F39" s="215"/>
+    </x:row>
+    <x:row r="40" ht="28" customHeight="1">
+      <x:c r="A40" s="212"/>
+      <x:c r="B40" s="212"/>
+      <x:c r="C40" s="212"/>
+      <x:c r="D40" s="277"/>
+      <x:c r="E40" s="212"/>
+      <x:c r="F40" s="212"/>
+    </x:row>
+    <x:row r="41" ht="28" customHeight="1">
+      <x:c r="A41" s="211" t="str">
+        <x:v>现金变动（十亿元）</x:v>
+      </x:c>
+      <x:c r="B41" s="211" t="str">
+        <x:v>2026H1</x:v>
+      </x:c>
+      <x:c r="C41" s="211" t="str">
+        <x:v>2026前三季</x:v>
+      </x:c>
+      <x:c r="D41" s="211" t="str">
+        <x:v>2026Q3</x:v>
+      </x:c>
+      <x:c r="E41" s="212"/>
+      <x:c r="F41" s="212"/>
+    </x:row>
+    <x:row r="42" ht="28" customHeight="1">
+      <x:c r="A42" s="212" t="str">
+        <x:v>经营现金流</x:v>
+      </x:c>
+      <x:c r="B42" s="213" t="n">
+        <x:v>1.3282460069</x:v>
+      </x:c>
+      <x:c r="C42" s="213" t="n">
+        <x:v>2.29470347516</x:v>
+      </x:c>
+      <x:c r="D42" s="278" t="n">
+        <x:f>C42-B42</x:f>
+        <x:v>0.96645746826</x:v>
+      </x:c>
+      <x:c r="E42" s="212"/>
+      <x:c r="F42" s="212"/>
+    </x:row>
+    <x:row r="43" ht="28" customHeight="1">
+      <x:c r="A43" s="212" t="str">
+        <x:v>现金购建长期资产</x:v>
+      </x:c>
+      <x:c r="B43" s="213" t="n">
+        <x:v>1.8006390221</x:v>
+      </x:c>
+      <x:c r="C43" s="213" t="n">
+        <x:v>2.09399359334</x:v>
+      </x:c>
+      <x:c r="D43" s="278" t="n">
+        <x:f>C43-B43</x:f>
+        <x:v>0.2933545712400001</x:v>
+      </x:c>
+      <x:c r="E43" s="212"/>
+      <x:c r="F43" s="212"/>
+    </x:row>
+    <x:row r="44" ht="28" customHeight="1">
+      <x:c r="A44" s="212" t="str">
+        <x:v>简化自由现金流</x:v>
+      </x:c>
+      <x:c r="B44" s="214" t="n">
+        <x:f>B42-B43</x:f>
+        <x:v>-0.4723930152</x:v>
+      </x:c>
+      <x:c r="C44" s="214" t="n">
+        <x:f>C42-C43</x:f>
+        <x:v>0.20070988181999994</x:v>
+      </x:c>
+      <x:c r="D44" s="278" t="n">
+        <x:f>D42-D43</x:f>
+        <x:v>0.6731028970199999</x:v>
+      </x:c>
+      <x:c r="E44" s="212"/>
+      <x:c r="F44" s="212"/>
+    </x:row>
+    <x:row r="45" ht="28" customHeight="1">
+      <x:c r="A45" s="212" t="str">
+        <x:v>投资现金流净额</x:v>
+      </x:c>
+      <x:c r="B45" s="213" t="n">
+        <x:v>0.05294789209</x:v>
+      </x:c>
+      <x:c r="C45" s="213" t="n">
+        <x:v>-2.04525842106</x:v>
+      </x:c>
+      <x:c r="D45" s="278" t="n">
+        <x:f>C45-B45</x:f>
+        <x:v>-2.0982063131500004</x:v>
+      </x:c>
+      <x:c r="E45" s="212"/>
+      <x:c r="F45" s="212"/>
+    </x:row>
+    <x:row r="46" ht="28" customHeight="1">
+      <x:c r="A46" s="212" t="str">
+        <x:v>筹资现金流净额</x:v>
+      </x:c>
+      <x:c r="B46" s="213" t="n">
+        <x:v>1.77924867683</x:v>
+      </x:c>
+      <x:c r="C46" s="213" t="n">
+        <x:v>0.70649222067</x:v>
+      </x:c>
+      <x:c r="D46" s="278" t="n">
+        <x:f>C46-B46</x:f>
+        <x:v>-1.07275645616</x:v>
+      </x:c>
+      <x:c r="E46" s="212"/>
+      <x:c r="F46" s="212"/>
+    </x:row>
+    <x:row r="47" ht="28" customHeight="1">
+      <x:c r="A47" s="212" t="str">
+        <x:v>汇率对现金影响</x:v>
+      </x:c>
+      <x:c r="B47" s="213" t="n">
+        <x:v>-0.06859608226</x:v>
+      </x:c>
+      <x:c r="C47" s="213" t="n">
+        <x:v>-0.07523236425</x:v>
+      </x:c>
+      <x:c r="D47" s="278" t="n">
+        <x:f>C47-B47</x:f>
+        <x:v>-0.006636281990000006</x:v>
+      </x:c>
+      <x:c r="E47" s="212"/>
+      <x:c r="F47" s="212"/>
+    </x:row>
+    <x:row r="48" ht="28" customHeight="1">
+      <x:c r="A48" s="212" t="str">
+        <x:v>现金净增减</x:v>
+      </x:c>
+      <x:c r="B48" s="214" t="n">
+        <x:f>SUM(B45:B47)+B42</x:f>
+        <x:v>3.09184649356</x:v>
+      </x:c>
+      <x:c r="C48" s="214" t="n">
+        <x:f>SUM(C45:C47)+C42</x:f>
+        <x:v>0.8807049105199998</x:v>
+      </x:c>
+      <x:c r="D48" s="278" t="n">
+        <x:f>SUM(D45:D47)+D42</x:f>
+        <x:v>-2.2111415830400007</x:v>
+      </x:c>
+      <x:c r="E48" s="212"/>
+      <x:c r="F48" s="212"/>
+    </x:row>
+    <x:row r="49" ht="28" customHeight="1">
+      <x:c r="A49" s="212" t="str">
+        <x:v>经营加投资现金流</x:v>
+      </x:c>
+      <x:c r="B49" s="214" t="n">
+        <x:f>B42+B45</x:f>
+        <x:v>1.38119389899</x:v>
+      </x:c>
+      <x:c r="C49" s="214" t="n">
+        <x:f>C42+C45</x:f>
+        <x:v>0.24944505409999973</x:v>
+      </x:c>
+      <x:c r="D49" s="278" t="n">
+        <x:f>D42+D45</x:f>
+        <x:v>-1.1317488448900004</x:v>
+      </x:c>
+      <x:c r="E49" s="212"/>
+      <x:c r="F49" s="212"/>
+    </x:row>
+    <x:row r="50" ht="28" customHeight="1">
+      <x:c r="A50" s="212" t="str">
+        <x:v>投资支付现金</x:v>
+      </x:c>
+      <x:c r="B50" s="213" t="n">
+        <x:v>3.17260007825</x:v>
+      </x:c>
+      <x:c r="C50" s="213" t="n">
+        <x:v>5.12419610516</x:v>
+      </x:c>
+      <x:c r="D50" s="278" t="n">
+        <x:f>C50-B50</x:f>
+        <x:v>1.9515960269100003</x:v>
+      </x:c>
+      <x:c r="E50" s="212"/>
+      <x:c r="F50" s="212"/>
+    </x:row>
+    <x:row r="51" ht="28" customHeight="1">
+      <x:c r="A51" s="212" t="str">
+        <x:v>取得投资收益现金</x:v>
+      </x:c>
+      <x:c r="B51" s="213" t="n">
+        <x:v>1.14420494007</x:v>
+      </x:c>
+      <x:c r="C51" s="213" t="n">
+        <x:v>1.15514233634</x:v>
+      </x:c>
+      <x:c r="D51" s="278" t="n">
+        <x:f>C51-B51</x:f>
+        <x:v>0.0109373962699999</x:v>
+      </x:c>
+      <x:c r="E51" s="212"/>
+      <x:c r="F51" s="212"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A39:F39"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2443,10 +3897,10 @@
         <x:v>A股收盘价</x:v>
       </x:c>
       <x:c r="B4" s="104" t="n">
-        <x:v>50.52</x:v>
+        <x:v>40.01</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>2026-09-04收盘</x:v>
+        <x:v>2026-10-15收盘，业绩公布前</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2454,7 +3908,7 @@
         <x:v>总股数</x:v>
       </x:c>
       <x:c r="B5" s="105" t="n">
-        <x:v>2.096694</x:v>
+        <x:v>2.096694404</x:v>
       </x:c>
       <x:c r="C5" s="19" t="str">
         <x:v>十亿股</x:v>
@@ -2466,7 +3920,7 @@
       </x:c>
       <x:c r="B6" s="67" t="n">
         <x:f>B4*B5</x:f>
-        <x:v>105.92498087999999</x:v>
+        <x:v>83.88874310403999</x:v>
       </x:c>
       <x:c r="C6" s="19" t="str">
         <x:v>RMB bn</x:v>
@@ -2477,10 +3931,10 @@
         <x:v>归母净资产</x:v>
       </x:c>
       <x:c r="B7" s="67" t="n">
-        <x:v>48.198717</x:v>
+        <x:v>48.12198173146</x:v>
       </x:c>
       <x:c r="C7" s="19" t="str">
-        <x:v>2026H1；RMB bn</x:v>
+        <x:v>2026Q3末；RMB bn</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2489,7 +3943,7 @@
       </x:c>
       <x:c r="B8" s="106" t="n">
         <x:f>B7/B5</x:f>
-        <x:v>22.987959616424718</x:v>
+        <x:v>22.95135697393696</x:v>
       </x:c>
       <x:c r="C8" s="19" t="str">
         <x:v>RMB/股</x:v>
@@ -2501,7 +3955,7 @@
       </x:c>
       <x:c r="B9" s="107" t="n">
         <x:f>B6/B7</x:f>
-        <x:v>2.1976722094075654</x:v>
+        <x:v>1.7432520458565672</x:v>
       </x:c>
       <x:c r="C9" s="22" t="str">
         <x:v>x</x:v>
@@ -2509,7 +3963,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="25" t="str">
-        <x:v>正常化驱动</x:v>
+        <x:v>2027正常化情景</x:v>
       </x:c>
       <x:c r="B12" s="26" t="str">
         <x:v>Bear</x:v>
@@ -2535,28 +3989,28 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="16" t="str">
-        <x:v>碳酸锂价格</x:v>
+        <x:v>碳酸锂情景中枢</x:v>
       </x:c>
       <x:c r="B13" s="102" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="102" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D13" s="102" t="n">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="D13" s="102" t="n">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="E13" s="16" t="str">
         <x:v>万元/吨</x:v>
       </x:c>
       <x:c r="F13" s="16" t="str">
-        <x:v>分析假设</x:v>
+        <x:v>研究情景</x:v>
       </x:c>
       <x:c r="G13" s="16" t="str">
-        <x:v>资源与锂盐盈利中枢</x:v>
+        <x:v>背景约束，不直接生成EPS</x:v>
       </x:c>
       <x:c r="H13" s="16" t="str">
-        <x:v>实际持续偏离情景假设</x:v>
+        <x:v>均价/成本需后续核实</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2564,94 +4018,94 @@
         <x:v>锂系列销量</x:v>
       </x:c>
       <x:c r="B14" s="103" t="n">
-        <x:v>180</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C14" s="103" t="n">
-        <x:v>220</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D14" s="103" t="n">
-        <x:v>260</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E14" s="19" t="str">
         <x:v>千吨LCE</x:v>
       </x:c>
       <x:c r="F14" s="19" t="str">
-        <x:v>分析假设</x:v>
+        <x:v>研究情景</x:v>
       </x:c>
       <x:c r="G14" s="19" t="str">
-        <x:v>多项目爬坡兑现</x:v>
+        <x:v>背景约束，不直接生成EPS</x:v>
       </x:c>
       <x:c r="H14" s="19" t="str">
-        <x:v>实际持续偏离情景假设</x:v>
+        <x:v>需销量与回收率验证</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="19" t="str">
         <x:v>电池毛利率</x:v>
       </x:c>
-      <x:c r="B15" s="103" t="n">
+      <x:c r="B15" s="216" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="C15" s="103" t="n">
+      <x:c r="C15" s="216" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="D15" s="103" t="n">
+      <x:c r="D15" s="216" t="n">
         <x:v>0.16</x:v>
       </x:c>
       <x:c r="E15" s="19" t="str">
         <x:v>比例</x:v>
       </x:c>
       <x:c r="F15" s="19" t="str">
-        <x:v>分析假设</x:v>
+        <x:v>研究情景</x:v>
       </x:c>
       <x:c r="G15" s="19" t="str">
-        <x:v>储能放量不等于高回报</x:v>
+        <x:v>H1毛利12.43%，Q3未披露</x:v>
       </x:c>
       <x:c r="H15" s="19" t="str">
-        <x:v>实际持续偏离情景假设</x:v>
+        <x:v>收入增长未带来现金回报</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="19" t="str">
-        <x:v>年度资本开支</x:v>
+        <x:v>年度现金购建</x:v>
       </x:c>
       <x:c r="B16" s="103" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C16" s="103" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D16" s="103" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E16" s="19" t="str">
         <x:v>RMB bn</x:v>
       </x:c>
       <x:c r="F16" s="19" t="str">
-        <x:v>分析假设</x:v>
+        <x:v>研究情景</x:v>
       </x:c>
       <x:c r="G16" s="19" t="str">
-        <x:v>自由现金流纪律</x:v>
+        <x:v>不含收购及金融投资</x:v>
       </x:c>
       <x:c r="H16" s="19" t="str">
-        <x:v>实际持续偏离情景假设</x:v>
+        <x:v>实际资本计划超出假设</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="19" t="str">
         <x:v>正常化归母净利润</x:v>
       </x:c>
-      <x:c r="B17" s="67" t="n">
-        <x:f>B18*$B$5</x:f>
-        <x:v>2.5160327999999996</x:v>
-      </x:c>
-      <x:c r="C17" s="67" t="n">
-        <x:f>C18*$B$5</x:f>
-        <x:v>5.870743199999999</x:v>
-      </x:c>
-      <x:c r="D17" s="67" t="n">
-        <x:f>D18*$B$5</x:f>
-        <x:v>9.435122999999999</x:v>
+      <x:c r="B17" s="170" t="n">
+        <x:f>IF(ISBLANK(B18),"n.a.",B18*$B$5)</x:f>
+        <x:v>2.096694404</x:v>
+      </x:c>
+      <x:c r="C17" s="170" t="n">
+        <x:f>IF(ISBLANK(C18),"n.a.",C18*$B$5)</x:f>
+        <x:v>5.0320665695999995</x:v>
+      </x:c>
+      <x:c r="D17" s="170" t="n">
+        <x:f>IF(ISBLANK(D18),"n.a.",D18*$B$5)</x:f>
+        <x:v>8.386777616</x:v>
       </x:c>
       <x:c r="E17" s="19" t="str">
         <x:v>RMB bn</x:v>
@@ -2671,13 +4125,13 @@
         <x:v>正常化EPS</x:v>
       </x:c>
       <x:c r="B18" s="114" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C18" s="114" t="n">
-        <x:v>2.8</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="D18" s="114" t="n">
-        <x:v>4.5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E18" s="19" t="str">
         <x:v>RMB/股</x:v>
@@ -2686,7 +4140,7 @@
         <x:v>分析假设</x:v>
       </x:c>
       <x:c r="G18" s="19" t="str">
-        <x:v>分析假设，非一致预期</x:v>
+        <x:v>2027正常化扣非EPS，主要输入</x:v>
       </x:c>
       <x:c r="H18" s="19" t="str">
         <x:v>实际持续偏离情景假设</x:v>
@@ -2697,13 +4151,13 @@
         <x:v>P/E</x:v>
       </x:c>
       <x:c r="B19" s="115" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C19" s="115" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D19" s="115" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E19" s="19" t="str">
         <x:v>x</x:v>
@@ -2712,7 +4166,7 @@
         <x:v>分析假设</x:v>
       </x:c>
       <x:c r="G19" s="19" t="str">
-        <x:v>增长期权与高杠杆折价</x:v>
+        <x:v>盈利放缓、融资负担约束</x:v>
       </x:c>
       <x:c r="H19" s="19" t="str">
         <x:v>实际持续偏离情景假设</x:v>
@@ -2723,13 +4177,13 @@
         <x:v>P/B</x:v>
       </x:c>
       <x:c r="B20" s="116" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C20" s="116" t="n">
-        <x:v>2</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D20" s="116" t="n">
-        <x:v>2.8</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="E20" s="22" t="str">
         <x:v>x</x:v>
@@ -2738,7 +4192,7 @@
         <x:v>分析假设</x:v>
       </x:c>
       <x:c r="G20" s="22" t="str">
-        <x:v>资产组合与项目执行交叉验证</x:v>
+        <x:v>账面价值与项目兑现折价</x:v>
       </x:c>
       <x:c r="H20" s="22" t="str">
         <x:v>实际持续偏离情景假设</x:v>
@@ -2749,7 +4203,7 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf62bd5fbccfd4d5e"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c9c225988544a86"/>
 </x:worksheet>
 </file>
 
@@ -2770,7 +4224,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>60% 正常化P/E + 40% P/B 情景估值</x:v>
+        <x:v>2027正常化P/E与P/B情景估值</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
         <x:v>60% 正常化P/E + 40% P/B 情景估值</x:v>
@@ -2830,111 +4284,111 @@
       <x:c r="A5" s="16" t="str">
         <x:v>Bear</x:v>
       </x:c>
-      <x:c r="B5" s="65" t="n">
+      <x:c r="B5" s="261" t="n">
         <x:f>'Assumptions'!B17</x:f>
-        <x:v>2.5160327999999996</x:v>
-      </x:c>
-      <x:c r="C5" s="136" t="n">
-        <x:f>'Assumptions'!B19</x:f>
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="137" t="n">
-        <x:f>B5*C5/'Assumptions'!$B$5</x:f>
-        <x:v>15.599999999999998</x:v>
-      </x:c>
-      <x:c r="E5" s="137" t="n">
+        <x:v>2.096694404</x:v>
+      </x:c>
+      <x:c r="C5" s="262" t="n">
+        <x:f>IF(ISBLANK('Assumptions'!B19),"n.a.",'Assumptions'!B19)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D5" s="263" t="n">
+        <x:f>IF(OR(B5="n.a.",C5="n.a."),"n.a.",B5*C5/'Assumptions'!$B$5)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E5" s="263" t="n">
         <x:f>'Assumptions'!$B$8</x:f>
-        <x:v>22.987959616424718</x:v>
-      </x:c>
-      <x:c r="F5" s="137" t="n">
-        <x:f>'Assumptions'!B20</x:f>
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="G5" s="137" t="n">
-        <x:f>E5*F5</x:f>
-        <x:v>27.58555153970966</x:v>
-      </x:c>
-      <x:c r="H5" s="138" t="n">
-        <x:f>D5*0.6+G5*0.4</x:f>
-        <x:v>20.39422061588386</x:v>
-      </x:c>
-      <x:c r="I5" s="74" t="n">
-        <x:f>H5/'Assumptions'!$B$4-1</x:f>
-        <x:v>-0.5963139228843258</x:v>
+        <x:v>22.95135697393696</x:v>
+      </x:c>
+      <x:c r="F5" s="263" t="n">
+        <x:f>IF(ISBLANK('Assumptions'!B20),"n.a.",'Assumptions'!B20)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="263" t="n">
+        <x:f>IF(F5="n.a.","n.a.",E5*F5)</x:f>
+        <x:v>22.95135697393696</x:v>
+      </x:c>
+      <x:c r="H5" s="163" t="n">
+        <x:f>IF(OR(D5="n.a.",G5="n.a."),"n.a.",D5*60%+G5*40%)</x:f>
+        <x:v>16.380542789574783</x:v>
+      </x:c>
+      <x:c r="I5" s="264" t="n">
+        <x:f>IF(H5="n.a.","n.a.",H5/'Assumptions'!$B$4-1)</x:f>
+        <x:v>-0.5905887830648642</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="139" t="str">
         <x:v>Base</x:v>
       </x:c>
-      <x:c r="B6" s="140" t="n">
+      <x:c r="B6" s="265" t="n">
         <x:f>'Assumptions'!C17</x:f>
-        <x:v>5.870743199999999</x:v>
-      </x:c>
-      <x:c r="C6" s="141" t="n">
-        <x:f>'Assumptions'!C19</x:f>
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D6" s="142" t="n">
-        <x:f>B6*C6/'Assumptions'!$B$5</x:f>
-        <x:v>44.8</x:v>
-      </x:c>
-      <x:c r="E6" s="142" t="n">
+        <x:v>5.0320665695999995</x:v>
+      </x:c>
+      <x:c r="C6" s="266" t="n">
+        <x:f>IF(ISBLANK('Assumptions'!C19),"n.a.",'Assumptions'!C19)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D6" s="267" t="n">
+        <x:f>IF(OR(B6="n.a.",C6="n.a."),"n.a.",B6*C6/'Assumptions'!$B$5)</x:f>
+        <x:v>35.99999999999999</x:v>
+      </x:c>
+      <x:c r="E6" s="267" t="n">
         <x:f>'Assumptions'!$B$8</x:f>
-        <x:v>22.987959616424718</x:v>
-      </x:c>
-      <x:c r="F6" s="142" t="n">
-        <x:f>'Assumptions'!C20</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G6" s="142" t="n">
-        <x:f>E6*F6</x:f>
-        <x:v>45.975919232849435</x:v>
-      </x:c>
-      <x:c r="H6" s="143" t="n">
-        <x:f>D6*0.6+G6*0.4</x:f>
-        <x:v>45.270367693139775</x:v>
-      </x:c>
-      <x:c r="I6" s="144" t="n">
-        <x:f>H6/'Assumptions'!$B$4-1</x:f>
-        <x:v>-0.10391196173515893</x:v>
+        <x:v>22.95135697393696</x:v>
+      </x:c>
+      <x:c r="F6" s="267" t="n">
+        <x:f>IF(ISBLANK('Assumptions'!C20),"n.a.",'Assumptions'!C20)</x:f>
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="G6" s="267" t="n">
+        <x:f>IF(F6="n.a.","n.a.",E6*F6)</x:f>
+        <x:v>41.31244255308653</x:v>
+      </x:c>
+      <x:c r="H6" s="268" t="n">
+        <x:f>IF(OR(D6="n.a.",G6="n.a."),"n.a.",D6*60%+G6*40%)</x:f>
+        <x:v>38.124977021234606</x:v>
+      </x:c>
+      <x:c r="I6" s="269" t="n">
+        <x:f>IF(H6="n.a.","n.a.",H6/'Assumptions'!$B$4-1)</x:f>
+        <x:v>-0.04711379602012977</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="22" t="str">
         <x:v>Bull</x:v>
       </x:c>
-      <x:c r="B7" s="69" t="n">
+      <x:c r="B7" s="270" t="n">
         <x:f>'Assumptions'!D17</x:f>
-        <x:v>9.435122999999999</x:v>
-      </x:c>
-      <x:c r="C7" s="145" t="n">
-        <x:f>'Assumptions'!D19</x:f>
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D7" s="146" t="n">
-        <x:f>B7*C7/'Assumptions'!$B$5</x:f>
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="E7" s="146" t="n">
+        <x:v>8.386777616</x:v>
+      </x:c>
+      <x:c r="C7" s="271" t="n">
+        <x:f>IF(ISBLANK('Assumptions'!D19),"n.a.",'Assumptions'!D19)</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="272" t="n">
+        <x:f>IF(OR(B7="n.a.",C7="n.a."),"n.a.",B7*C7/'Assumptions'!$B$5)</x:f>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E7" s="272" t="n">
         <x:f>'Assumptions'!$B$8</x:f>
-        <x:v>22.987959616424718</x:v>
-      </x:c>
-      <x:c r="F7" s="146" t="n">
-        <x:f>'Assumptions'!D20</x:f>
-        <x:v>2.8</x:v>
-      </x:c>
-      <x:c r="G7" s="146" t="n">
-        <x:f>E7*F7</x:f>
-        <x:v>64.3662869259892</x:v>
-      </x:c>
-      <x:c r="H7" s="147" t="n">
-        <x:f>D7*0.6+G7*0.4</x:f>
-        <x:v>74.34651477039569</x:v>
-      </x:c>
-      <x:c r="I7" s="76" t="n">
-        <x:f>H7/'Assumptions'!$B$4-1</x:f>
-        <x:v>0.4716253913379984</x:v>
+        <x:v>22.95135697393696</x:v>
+      </x:c>
+      <x:c r="F7" s="272" t="n">
+        <x:f>IF(ISBLANK('Assumptions'!D20),"n.a.",'Assumptions'!D20)</x:f>
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="G7" s="272" t="n">
+        <x:f>IF(F7="n.a.","n.a.",E7*F7)</x:f>
+        <x:v>57.3783924348424</x:v>
+      </x:c>
+      <x:c r="H7" s="273" t="n">
+        <x:f>IF(OR(D7="n.a.",G7="n.a."),"n.a.",D7*60%+G7*40%)</x:f>
+        <x:v>63.75135697393696</x:v>
+      </x:c>
+      <x:c r="I7" s="274" t="n">
+        <x:f>IF(H7="n.a.","n.a.",H7/'Assumptions'!$B$4-1)</x:f>
+        <x:v>0.5933855779539354</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3144,7 +4598,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="52" t="str">
-        <x:v>正常化盈利、商品价格、产销量、资本开支与估值倍数均为分析情景，不是公司指引或市场一致预期。模型不把2026H1高景气利润直接年化；P/B只作资本密集型周期股的交叉验证，账面价值仍受减值、汇率、项目执行及关联资产可变现性影响。</x:v>
+        <x:v>主估值延续60%正常化P/E+40%P/B。P/E反映盈利，P/B约束资本密集且利润波动的项目资产；二者相关，不是独立证据。净债务已影响利润和权益，不再重复扣。商品价格和产销量仅为背景校准，尚无完整单位成本模型，EPS为研究假设。</x:v>
       </x:c>
       <x:c r="B20" s="52" t="str">
         <x:v>正常化盈利、商品价格、产销量、资本开支与估值倍数均为分析情景，不是公司指引或市场一致预期。模型不把2026H1高景气利润直接年化；P/B只作资本密集型周期股的交叉验证，账面价值仍受减值、汇率、项目执行及关联资产可变现性影响。</x:v>
@@ -3315,6 +4769,121 @@
       <x:c r="I25" s="52" t="str">
         <x:v>正常化盈利、商品价格、产销量、资本开支与估值倍数均为分析情景，不是公司指引或市场一致预期。模型不把2026H1高景气利润直接年化；P/B只作资本密集型周期股的交叉验证，账面价值仍受减值、汇率、项目执行及关联资产可变现性影响。</x:v>
       </x:c>
+    </x:row>
+    <x:row r="28" ht="27" customHeight="1">
+      <x:c r="A28" s="211" t="str">
+        <x:v>最新参考指标</x:v>
+      </x:c>
+      <x:c r="B28" s="211" t="str">
+        <x:v>数值</x:v>
+      </x:c>
+      <x:c r="C28" s="211" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+      <x:c r="D28" s="212"/>
+      <x:c r="E28" s="212"/>
+      <x:c r="F28" s="212"/>
+      <x:c r="G28" s="212"/>
+      <x:c r="H28" s="212"/>
+      <x:c r="I28" s="212"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="212" t="str">
+        <x:v>TTM归母利润</x:v>
+      </x:c>
+      <x:c r="B29" s="275" t="n">
+        <x:f>'Historical'!B35-'Historical'!C35+'Historical'!D35</x:f>
+        <x:v>6.59972041749</x:v>
+      </x:c>
+      <x:c r="C29" s="212"/>
+      <x:c r="D29" s="212"/>
+      <x:c r="E29" s="212"/>
+      <x:c r="F29" s="212"/>
+      <x:c r="G29" s="212"/>
+      <x:c r="H29" s="212"/>
+      <x:c r="I29" s="212"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="212" t="str">
+        <x:v>TTM扣非归母</x:v>
+      </x:c>
+      <x:c r="B30" s="275" t="n">
+        <x:f>'Historical'!B36-'Historical'!C36+'Historical'!D36</x:f>
+        <x:v>5.19241343527</x:v>
+      </x:c>
+      <x:c r="C30" s="212"/>
+      <x:c r="D30" s="212"/>
+      <x:c r="E30" s="212"/>
+      <x:c r="F30" s="212"/>
+      <x:c r="G30" s="212"/>
+      <x:c r="H30" s="212"/>
+      <x:c r="I30" s="212"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="212" t="str">
+        <x:v>A价等价扣非P/E</x:v>
+      </x:c>
+      <x:c r="B31" s="275" t="n">
+        <x:f>'Assumptions'!B6/B30</x:f>
+        <x:v>16.15602150133445</x:v>
+      </x:c>
+      <x:c r="C31" s="212" t="str">
+        <x:v>A价×总股本，非A/H合计市值</x:v>
+      </x:c>
+      <x:c r="D31" s="212"/>
+      <x:c r="E31" s="212"/>
+      <x:c r="F31" s="212"/>
+      <x:c r="G31" s="212"/>
+      <x:c r="H31" s="212"/>
+      <x:c r="I31" s="212"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="212" t="str">
+        <x:v>P/E单独基准价值</x:v>
+      </x:c>
+      <x:c r="B32" s="275" t="n">
+        <x:f>D6</x:f>
+        <x:v>35.99999999999999</x:v>
+      </x:c>
+      <x:c r="C32" s="212"/>
+      <x:c r="D32" s="212"/>
+      <x:c r="E32" s="212"/>
+      <x:c r="F32" s="212"/>
+      <x:c r="G32" s="212"/>
+      <x:c r="H32" s="212"/>
+      <x:c r="I32" s="212"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="212" t="str">
+        <x:v>P/B单独基准价值</x:v>
+      </x:c>
+      <x:c r="B33" s="275" t="n">
+        <x:f>G6</x:f>
+        <x:v>41.31244255308653</x:v>
+      </x:c>
+      <x:c r="C33" s="212"/>
+      <x:c r="D33" s="212"/>
+      <x:c r="E33" s="212"/>
+      <x:c r="F33" s="212"/>
+      <x:c r="G33" s="212"/>
+      <x:c r="H33" s="212"/>
+      <x:c r="I33" s="212"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="212" t="str">
+        <x:v>P/E权重升至75%</x:v>
+      </x:c>
+      <x:c r="B34" s="275" t="n">
+        <x:f>D6*75%+G6*25%</x:f>
+        <x:v>37.328110638271625</x:v>
+      </x:c>
+      <x:c r="C34" s="212"/>
+      <x:c r="D34" s="212"/>
+      <x:c r="E34" s="212"/>
+      <x:c r="F34" s="212"/>
+      <x:c r="G34" s="212"/>
+      <x:c r="H34" s="212"/>
+      <x:c r="I34" s="212"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3391,8 +4960,8 @@
       <x:c r="E2" t="str">
         <x:v>总体模型状态</x:v>
       </x:c>
-      <x:c r="F2" t="str">
-        <x:f>IF(COUNTIF(F5:F13,"FAIL")=0,"OK","FAIL")</x:f>
+      <x:c r="F2" s="172" t="str">
+        <x:f>IF(COUNTIF(F5:F24,"FAIL")=0,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
@@ -3425,21 +4994,21 @@
       </x:c>
       <x:c r="B5" s="16" t="n">
         <x:f>'Assumptions'!B6</x:f>
-        <x:v>105.92498087999999</x:v>
+        <x:v>83.88874310403999</x:v>
       </x:c>
       <x:c r="C5" s="16" t="n">
         <x:f>'Assumptions'!B4*'Assumptions'!B5</x:f>
-        <x:v>105.92498087999999</x:v>
-      </x:c>
-      <x:c r="D5" s="16" t="n">
+        <x:v>83.88874310403999</x:v>
+      </x:c>
+      <x:c r="D5" s="240" t="n">
         <x:f>B5-C5</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="n">
+      <x:c r="E5" s="241" t="n">
         <x:f>0.0001</x:f>
         <x:v>0.0001</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="str">
+      <x:c r="F5" s="241" t="str">
         <x:f>IF(ABS(D5)&lt;=E5,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -3453,21 +5022,21 @@
       </x:c>
       <x:c r="B6" s="19" t="n">
         <x:f>'Assumptions'!B8</x:f>
-        <x:v>22.987959616424718</x:v>
+        <x:v>22.95135697393696</x:v>
       </x:c>
       <x:c r="C6" s="19" t="n">
         <x:f>'Assumptions'!B7/'Assumptions'!B5</x:f>
-        <x:v>22.987959616424718</x:v>
-      </x:c>
-      <x:c r="D6" s="19" t="n">
+        <x:v>22.95135697393696</x:v>
+      </x:c>
+      <x:c r="D6" s="242" t="n">
         <x:f>B6-C6</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="n">
+      <x:c r="E6" s="243" t="n">
         <x:f>0.0001</x:f>
         <x:v>0.0001</x:v>
       </x:c>
-      <x:c r="F6" s="19" t="str">
+      <x:c r="F6" s="243" t="str">
         <x:f>IF(ABS(D6)&lt;=E6,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -3481,21 +5050,21 @@
       </x:c>
       <x:c r="B7" s="19" t="n">
         <x:f>'Assumptions'!B9</x:f>
-        <x:v>2.1976722094075654</x:v>
+        <x:v>1.7432520458565672</x:v>
       </x:c>
       <x:c r="C7" s="19" t="n">
         <x:f>'Assumptions'!B6/'Assumptions'!B7</x:f>
-        <x:v>2.1976722094075654</x:v>
-      </x:c>
-      <x:c r="D7" s="19" t="n">
+        <x:v>1.7432520458565672</x:v>
+      </x:c>
+      <x:c r="D7" s="242" t="n">
         <x:f>B7-C7</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E7" s="19" t="n">
+      <x:c r="E7" s="243" t="n">
         <x:f>0.0001</x:f>
         <x:v>0.0001</x:v>
       </x:c>
-      <x:c r="F7" s="19" t="str">
+      <x:c r="F7" s="243" t="str">
         <x:f>IF(ABS(D7)&lt;=E7,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -3509,21 +5078,21 @@
       </x:c>
       <x:c r="B8" s="19" t="n">
         <x:f>'Balance &amp; Cash'!B22</x:f>
-        <x:v>-1.1067869999999997</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="n">
-        <x:f>'Historical'!E7-'Historical'!F7</x:f>
-        <x:v>-1.1067869999999997</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="n">
+        <x:v>0.20070988181999994</x:v>
+      </x:c>
+      <x:c r="C8" s="232" t="n">
+        <x:f>'Historical'!E8-'Historical'!F8</x:f>
+        <x:v>0.20070988181999994</x:v>
+      </x:c>
+      <x:c r="D8" s="242" t="n">
         <x:f>B8-C8</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="n">
+      <x:c r="E8" s="243" t="n">
         <x:f>0.0001</x:f>
         <x:v>0.0001</x:v>
       </x:c>
-      <x:c r="F8" s="19" t="str">
+      <x:c r="F8" s="243" t="str">
         <x:f>IF(ABS(D8)&lt;=E8,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -3533,30 +5102,30 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="19" t="str">
-        <x:v>净债务桥</x:v>
+        <x:v>融资净负担桥</x:v>
       </x:c>
       <x:c r="B9" s="19" t="n">
         <x:f>'Balance &amp; Cash'!B15</x:f>
-        <x:v>25.736899</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="n">
-        <x:f>'Balance &amp; Cash'!B9+'Balance &amp; Cash'!B10+'Balance &amp; Cash'!B11-'Balance &amp; Cash'!B7</x:f>
-        <x:v>25.736899</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="n">
+        <x:v>32.16101889704</x:v>
+      </x:c>
+      <x:c r="C9" s="232" t="n">
+        <x:f>SUM('Balance &amp; Cash'!C28:C33)-'Balance &amp; Cash'!C34</x:f>
+        <x:v>32.16101889704</x:v>
+      </x:c>
+      <x:c r="D9" s="242" t="n">
         <x:f>B9-C9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E9" s="19" t="n">
+      <x:c r="E9" s="243" t="n">
         <x:f>0.0001</x:f>
         <x:v>0.0001</x:v>
       </x:c>
-      <x:c r="F9" s="19" t="str">
+      <x:c r="F9" s="243" t="str">
         <x:f>IF(ABS(D9)&lt;=E9,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G9" s="19" t="str">
-        <x:v>借款+债券+租赁-现金</x:v>
+        <x:v>含长期应付款，未纳其他流动项</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3565,21 +5134,21 @@
       </x:c>
       <x:c r="B10" s="19" t="n">
         <x:f>'Valuation'!H6</x:f>
-        <x:v>45.270367693139775</x:v>
+        <x:v>38.124977021234606</x:v>
       </x:c>
       <x:c r="C10" s="19" t="n">
         <x:f>'Valuation'!D6*0.6+'Valuation'!G6*0.4</x:f>
-        <x:v>45.270367693139775</x:v>
-      </x:c>
-      <x:c r="D10" s="19" t="n">
+        <x:v>38.124977021234606</x:v>
+      </x:c>
+      <x:c r="D10" s="242" t="n">
         <x:f>B10-C10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="19" t="n">
+      <x:c r="E10" s="243" t="n">
         <x:f>0.0001</x:f>
         <x:v>0.0001</x:v>
       </x:c>
-      <x:c r="F10" s="19" t="str">
+      <x:c r="F10" s="243" t="str">
         <x:f>IF(ABS(D10)&lt;=E10,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -3599,15 +5168,15 @@
         <x:f>100%</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D11" s="19" t="n">
+      <x:c r="D11" s="242" t="n">
         <x:f>B11-C11</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="19" t="n">
+      <x:c r="E11" s="243" t="n">
         <x:f>0.0001</x:f>
         <x:v>0.0001</x:v>
       </x:c>
-      <x:c r="F11" s="19" t="str">
+      <x:c r="F11" s="243" t="str">
         <x:f>IF(ABS(D11)&lt;=E11,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -3621,21 +5190,21 @@
       </x:c>
       <x:c r="B12" s="19" t="n">
         <x:f>'Assumptions'!D17-'Assumptions'!B17</x:f>
-        <x:v>6.919090199999999</x:v>
+        <x:v>6.290083212</x:v>
       </x:c>
       <x:c r="C12" s="19" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="19" t="n">
+      <x:c r="D12" s="242" t="n">
         <x:f>B12-C12</x:f>
-        <x:v>6.919090199999999</x:v>
-      </x:c>
-      <x:c r="E12" s="19" t="n">
+        <x:v>6.290083212</x:v>
+      </x:c>
+      <x:c r="E12" s="243" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="19" t="str">
+      <x:c r="F12" s="243" t="str">
         <x:f>IF(B12&gt;C12,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
@@ -3649,26 +5218,312 @@
       </x:c>
       <x:c r="B13" s="22" t="n">
         <x:f>'Valuation'!H7-'Valuation'!H5</x:f>
-        <x:v>53.952294154511826</x:v>
+        <x:v>47.370814184362175</x:v>
       </x:c>
       <x:c r="C13" s="22" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D13" s="22" t="n">
+      <x:c r="D13" s="244" t="n">
         <x:f>B13-C13</x:f>
-        <x:v>53.952294154511826</x:v>
-      </x:c>
-      <x:c r="E13" s="22" t="n">
+        <x:v>47.370814184362175</x:v>
+      </x:c>
+      <x:c r="E13" s="245" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="22" t="str">
+      <x:c r="F13" s="245" t="str">
         <x:f>IF(B13&gt;C13,"OK","FAIL")</x:f>
         <x:v>OK</x:v>
       </x:c>
       <x:c r="G13" s="22" t="str">
         <x:v>Bull高于Bear</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="212" t="str">
+        <x:v>Q3收入累计差核对</x:v>
+      </x:c>
+      <x:c r="B14" s="256" t="n">
+        <x:f>'Historical'!B20</x:f>
+        <x:v>13.061786733240002</x:v>
+      </x:c>
+      <x:c r="C14" s="257" t="n">
+        <x:v>13.06178673324</x:v>
+      </x:c>
+      <x:c r="D14" s="258" t="n">
+        <x:f>ROUND(B14-C14,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F14" s="260" t="str">
+        <x:f>IF(ABS(D14)&lt;=E14,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G14" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="212" t="str">
+        <x:v>Q3归母累计差核对</x:v>
+      </x:c>
+      <x:c r="B15" s="256" t="n">
+        <x:f>'Historical'!C20</x:f>
+        <x:v>0.7550945993700005</x:v>
+      </x:c>
+      <x:c r="C15" s="257" t="n">
+        <x:v>0.75509459937</x:v>
+      </x:c>
+      <x:c r="D15" s="258" t="n">
+        <x:f>ROUND(B15-C15,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F15" s="260" t="str">
+        <x:f>IF(ABS(D15)&lt;=E15,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G15" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="212" t="str">
+        <x:v>Q3扣非累计差核对</x:v>
+      </x:c>
+      <x:c r="B16" s="256" t="n">
+        <x:f>'Historical'!D20</x:f>
+        <x:v>0.7876437739199997</x:v>
+      </x:c>
+      <x:c r="C16" s="257" t="n">
+        <x:v>0.78764377392</x:v>
+      </x:c>
+      <x:c r="D16" s="258" t="n">
+        <x:f>ROUND(B16-C16,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F16" s="260" t="str">
+        <x:f>IF(ABS(D16)&lt;=E16,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G16" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="212" t="str">
+        <x:v>前三季非经常损益桥</x:v>
+      </x:c>
+      <x:c r="B17" s="256" t="n">
+        <x:f>'Historical'!C8-'Historical'!D8</x:f>
+        <x:v>0.37638994716000074</x:v>
+      </x:c>
+      <x:c r="C17" s="257" t="n">
+        <x:v>0.37638994716</x:v>
+      </x:c>
+      <x:c r="D17" s="258" t="n">
+        <x:f>ROUND(B17-C17,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F17" s="260" t="str">
+        <x:f>IF(ABS(D17)&lt;=E17,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G17" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="212" t="str">
+        <x:v>前三季购建现金原件</x:v>
+      </x:c>
+      <x:c r="B18" s="256" t="n">
+        <x:f>'Historical'!F8</x:f>
+        <x:v>2.09399359334</x:v>
+      </x:c>
+      <x:c r="C18" s="257" t="n">
+        <x:v>2.09399359334</x:v>
+      </x:c>
+      <x:c r="D18" s="258" t="n">
+        <x:f>ROUND(B18-C18,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F18" s="260" t="str">
+        <x:f>IF(ABS(D18)&lt;=E18,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G18" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="212" t="str">
+        <x:v>H1现金购建原件修正</x:v>
+      </x:c>
+      <x:c r="B19" s="256" t="n">
+        <x:f>'Historical'!F7</x:f>
+        <x:v>1.8006390221</x:v>
+      </x:c>
+      <x:c r="C19" s="257" t="n">
+        <x:v>1.8006390221</x:v>
+      </x:c>
+      <x:c r="D19" s="258" t="n">
+        <x:f>ROUND(B19-C19,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F19" s="260" t="str">
+        <x:f>IF(ABS(D19)&lt;=E19,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G19" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="212" t="str">
+        <x:v>融资负担独立核对</x:v>
+      </x:c>
+      <x:c r="B20" s="256" t="n">
+        <x:f>'Balance &amp; Cash'!B15</x:f>
+        <x:v>32.16101889704</x:v>
+      </x:c>
+      <x:c r="C20" s="257" t="n">
+        <x:v>32.16101889704</x:v>
+      </x:c>
+      <x:c r="D20" s="258" t="n">
+        <x:f>ROUND(B20-C20,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F20" s="260" t="str">
+        <x:f>IF(ABS(D20)&lt;=E20,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G20" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="212" t="str">
+        <x:v>期末现金变动核对</x:v>
+      </x:c>
+      <x:c r="B21" s="256" t="n">
+        <x:f>'Balance &amp; Cash'!C48</x:f>
+        <x:v>0.8807049105199998</x:v>
+      </x:c>
+      <x:c r="C21" s="257" t="n">
+        <x:v>0.88070491052</x:v>
+      </x:c>
+      <x:c r="D21" s="258" t="n">
+        <x:f>ROUND(B21-C21,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F21" s="260" t="str">
+        <x:f>IF(ABS(D21)&lt;=E21,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G21" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="212" t="str">
+        <x:v>A/H股份合计</x:v>
+      </x:c>
+      <x:c r="B22" s="256" t="n">
+        <x:f>'Assumptions'!B5</x:f>
+        <x:v>2.096694404</x:v>
+      </x:c>
+      <x:c r="C22" s="257" t="n">
+        <x:v>2.096694404</x:v>
+      </x:c>
+      <x:c r="D22" s="258" t="n">
+        <x:f>ROUND(B22-C22,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F22" s="260" t="str">
+        <x:f>IF(ABS(D22)&lt;=E22,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G22" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="212" t="str">
+        <x:v>Q3现金变化桥</x:v>
+      </x:c>
+      <x:c r="B23" s="256" t="n">
+        <x:f>'Balance &amp; Cash'!D48</x:f>
+        <x:v>-2.2111415830400007</x:v>
+      </x:c>
+      <x:c r="C23" s="257" t="n">
+        <x:v>-2.21114158304</x:v>
+      </x:c>
+      <x:c r="D23" s="258" t="n">
+        <x:f>ROUND(B23-C23,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F23" s="260" t="str">
+        <x:f>IF(ABS(D23)&lt;=E23,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G23" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="212" t="str">
+        <x:v>H1公司净负债披露</x:v>
+      </x:c>
+      <x:c r="B24" s="256" t="n">
+        <x:f>'Balance &amp; Cash'!B38</x:f>
+        <x:v>29.25100542454</x:v>
+      </x:c>
+      <x:c r="C24" s="257" t="n">
+        <x:v>29.25100542454</x:v>
+      </x:c>
+      <x:c r="D24" s="258" t="n">
+        <x:f>ROUND(B24-C24,6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="259" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F24" s="260" t="str">
+        <x:f>IF(ABS(D24)&lt;=E24,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G24" s="212" t="str">
+        <x:v>来源原件/独立重算</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3679,6 +5534,16 @@
   <x:conditionalFormatting sqref="F2:F13">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="OK"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="FAIL"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D5:D11">
+    <x:cfRule type="expression" dxfId="3" priority="3">
+      <x:formula>ABS(D5)&gt;0.000001</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D14:D24">
+    <x:cfRule type="expression" dxfId="4" priority="4">
+      <x:formula>ABS(D14)&gt;0.000001</x:formula>
+    </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3753,7 +5618,7 @@
         <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0828/2026082803928.pdf</x:v>
       </x:c>
       <x:c r="F4" s="157" t="str">
-        <x:v>官方；未经审计；本地已归档</x:v>
+        <x:v>IFRS仅用于业务与资本新增；现金流改用CAS</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
@@ -3773,7 +5638,7 @@
         <x:v>https://www.hkexnews.hk/listedco/listconews/sehk/2026/0430/2026043002397_c.pdf</x:v>
       </x:c>
       <x:c r="F5" s="159" t="str">
-        <x:v>官方；经审计；本地已归档</x:v>
+        <x:v>历史原件保留；年度财务现统一CAS</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="44" customHeight="1">
@@ -3804,16 +5669,16 @@
         <x:v>A股收盘价</x:v>
       </x:c>
       <x:c r="C7" s="159" t="str">
-        <x:v>公开市场行情</x:v>
+        <x:v>Investing及观势</x:v>
       </x:c>
       <x:c r="D7" s="159" t="str">
-        <x:v>2026-09-04</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="E7" s="160" t="str">
-        <x:v>https://stockinvest.us/stock-price/002460.SZ</x:v>
+        <x:v>https://cn.investing.com/equities/ganfeng-lithium-a-historical-data</x:v>
       </x:c>
       <x:c r="F7" s="159" t="str">
-        <x:v>二级市场数据；50.52元</x:v>
+        <x:v>40.01元，闭盘，业绩公布前</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
@@ -3833,7 +5698,7 @@
         <x:v>https://www.9qihuo.com/hangqing?shichang=GFEX</x:v>
       </x:c>
       <x:c r="F8" s="159" t="str">
-        <x:v>主力约14.2万元/吨；高波动</x:v>
+        <x:v>历史背景，仅2026-09-04，不作为当前锂价</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
@@ -3883,11 +5748,191 @@
         <x:v>研究计算</x:v>
       </x:c>
       <x:c r="D11" s="161" t="str">
-        <x:v>2026H1</x:v>
+        <x:v>2026Q3</x:v>
       </x:c>
       <x:c r="E11" s="161" t="str"/>
       <x:c r="F11" s="161" t="str">
         <x:v>按模型公式计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="55" customHeight="1">
+      <x:c r="A13" s="250" t="str">
+        <x:v>N1</x:v>
+      </x:c>
+      <x:c r="B13" s="250" t="str">
+        <x:v>2026年第三季度报告</x:v>
+      </x:c>
+      <x:c r="C13" s="250" t="str">
+        <x:v>公司正式公告</x:v>
+      </x:c>
+      <x:c r="D13" s="250" t="str">
+        <x:v>15日晚获取，落款16日</x:v>
+      </x:c>
+      <x:c r="E13" s="250" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-10-16/1225607211.PDF</x:v>
+      </x:c>
+      <x:c r="F13" s="250" t="str">
+        <x:v>本地原件：12页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="55" customHeight="1">
+      <x:c r="A14" s="250" t="str">
+        <x:v>N2</x:v>
+      </x:c>
+      <x:c r="B14" s="250" t="str">
+        <x:v>第六届董事会第二十二次决议</x:v>
+      </x:c>
+      <x:c r="C14" s="250" t="str">
+        <x:v>公司正式公告</x:v>
+      </x:c>
+      <x:c r="D14" s="250" t="str">
+        <x:v>15日晚获取，落款16日</x:v>
+      </x:c>
+      <x:c r="E14" s="250" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-10-16/1225607212.PDF</x:v>
+      </x:c>
+      <x:c r="F14" s="250" t="str">
+        <x:v>本地原件：2页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="55" customHeight="1">
+      <x:c r="A15" s="250" t="str">
+        <x:v>N3</x:v>
+      </x:c>
+      <x:c r="B15" s="250" t="str">
+        <x:v>增加关联担保额度</x:v>
+      </x:c>
+      <x:c r="C15" s="250" t="str">
+        <x:v>公司正式公告</x:v>
+      </x:c>
+      <x:c r="D15" s="250" t="str">
+        <x:v>15日晚获取，落款16日</x:v>
+      </x:c>
+      <x:c r="E15" s="250" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-10-16/1225607214.PDF</x:v>
+      </x:c>
+      <x:c r="F15" s="250" t="str">
+        <x:v>本地原件：7页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="55" customHeight="1">
+      <x:c r="A16" s="250" t="str">
+        <x:v>N4</x:v>
+      </x:c>
+      <x:c r="B16" s="250" t="str">
+        <x:v>对控股子公司担保进展</x:v>
+      </x:c>
+      <x:c r="C16" s="250" t="str">
+        <x:v>公司正式公告</x:v>
+      </x:c>
+      <x:c r="D16" s="250" t="str">
+        <x:v>15日晚获取，落款16日</x:v>
+      </x:c>
+      <x:c r="E16" s="250" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-10-16/1225607213.PDF</x:v>
+      </x:c>
+      <x:c r="F16" s="250" t="str">
+        <x:v>本地原件：4页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="55" customHeight="1">
+      <x:c r="A17" s="250" t="str">
+        <x:v>N5</x:v>
+      </x:c>
+      <x:c r="B17" s="250" t="str">
+        <x:v>2026半年度报告（CAS）</x:v>
+      </x:c>
+      <x:c r="C17" s="250" t="str">
+        <x:v>公司正式公告</x:v>
+      </x:c>
+      <x:c r="D17" s="250" t="str">
+        <x:v>见文件日期</x:v>
+      </x:c>
+      <x:c r="E17" s="250" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-08-28/1225533700.PDF</x:v>
+      </x:c>
+      <x:c r="F17" s="250" t="str">
+        <x:v>本地原件：225页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="55" customHeight="1">
+      <x:c r="A18" s="250" t="str">
+        <x:v>N6</x:v>
+      </x:c>
+      <x:c r="B18" s="250" t="str">
+        <x:v>2026第一季度报告（CAS）</x:v>
+      </x:c>
+      <x:c r="C18" s="250" t="str">
+        <x:v>公司正式公告</x:v>
+      </x:c>
+      <x:c r="D18" s="250" t="str">
+        <x:v>见文件日期</x:v>
+      </x:c>
+      <x:c r="E18" s="250" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-04-30/1225255341.PDF</x:v>
+      </x:c>
+      <x:c r="F18" s="250" t="str">
+        <x:v>本地原件：11页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="55" customHeight="1">
+      <x:c r="A19" s="250" t="str">
+        <x:v>N7</x:v>
+      </x:c>
+      <x:c r="B19" s="250" t="str">
+        <x:v>2025年度报告（CAS）</x:v>
+      </x:c>
+      <x:c r="C19" s="250" t="str">
+        <x:v>公司正式公告</x:v>
+      </x:c>
+      <x:c r="D19" s="250" t="str">
+        <x:v>见文件日期</x:v>
+      </x:c>
+      <x:c r="E19" s="250" t="str">
+        <x:v>https://www.hkexnews.hk/listedco/listconews/sehk/2026/0331/2026033100487_c.pdf</x:v>
+      </x:c>
+      <x:c r="F19" s="250" t="str">
+        <x:v>本地原件：277页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="55" customHeight="1">
+      <x:c r="A20" s="250" t="str">
+        <x:v>N8</x:v>
+      </x:c>
+      <x:c r="B20" s="250" t="str">
+        <x:v>2026年9月股份月报</x:v>
+      </x:c>
+      <x:c r="C20" s="250" t="str">
+        <x:v>公司正式公告</x:v>
+      </x:c>
+      <x:c r="D20" s="250" t="str">
+        <x:v>见文件日期</x:v>
+      </x:c>
+      <x:c r="E20" s="250" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-10-08/1225590578.PDF</x:v>
+      </x:c>
+      <x:c r="F20" s="250" t="str">
+        <x:v>本地原件：10页</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="55" customHeight="1">
+      <x:c r="A21" s="250" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+      <x:c r="B21" s="250" t="str">
+        <x:v>收盘行情交叉核对</x:v>
+      </x:c>
+      <x:c r="C21" s="250" t="str">
+        <x:v>观势</x:v>
+      </x:c>
+      <x:c r="D21" s="250" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="E21" s="250" t="str">
+        <x:v>https://www.lvzen.top/stock/002460.html</x:v>
+      </x:c>
+      <x:c r="F21" s="250" t="str">
+        <x:v>仅用价格，不采页面估值</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
